--- a/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
+++ b/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
@@ -80,7 +80,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -219,6 +219,12 @@
       <b val="1"/>
       <color rgb="00D9D9D9"/>
       <sz val="26"/>
+    </font>
+    <font>
+      <name val="Arial Black"/>
+      <b val="1"/>
+      <color rgb="00D9D9D9"/>
+      <sz val="48"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -657,7 +663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -943,8 +949,11 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3418,11 +3427,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3535,11 +3544,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3610,11 +3619,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
         <v/>
       </c>
     </row>
@@ -3656,11 +3665,11 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E35" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68))</f>
         <v/>
       </c>
     </row>
@@ -4048,11 +4057,11 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E16" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4219,11 +4228,11 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E23" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4269,11 +4278,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4461,11 +4470,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4486,11 +4495,11 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E34" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4688,7 +4697,7 @@
         </is>
       </c>
       <c r="D9" s="101">
-        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E9" s="102" t="n"/>
@@ -4934,7 +4943,7 @@
         </is>
       </c>
       <c r="D25" s="84">
-        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
+        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
         <v/>
       </c>
       <c r="E25" s="85" t="n"/>
@@ -5075,7 +5084,7 @@
         </is>
       </c>
       <c r="D34" s="9">
-        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
+        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
         <v/>
       </c>
       <c r="E34" s="82" t="n"/>
@@ -5097,7 +5106,7 @@
         </is>
       </c>
       <c r="D35" s="101">
-        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68))))-D9</f>
+        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))))-D9</f>
         <v/>
       </c>
       <c r="E35" s="102" t="n"/>
@@ -6575,7 +6584,7 @@
       </c>
       <c r="B17" s="119" t="inlineStr"/>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
@@ -6739,7 +6748,7 @@
         </is>
       </c>
       <c r="C26" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D26" s="120" t="n"/>
@@ -6954,14 +6963,14 @@
       </c>
     </row>
     <row r="47"/>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="114">
-        <f>IF(SUM(B33:B44,C10:C44,D10:D36,E10:E26,F10:F26)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="26" customHeight="1"/>
-    <row r="50" ht="26" customHeight="1"/>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="122">
+        <f>IF(SUM(B33:B44,C10:C44,D10:D36,E10:E26,F10:F26)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1"/>
+    <row r="50" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E2:F2"/>
@@ -7069,7 +7078,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>A - IDENTITÉ, ORGANISATION : décrire brièvement l'identité de l'entité (date de création, nature du projet associatif, mission) et l'organisation avec des données chiffrées (effectifs, nombre de bénévoles, total des revenus, moyens utilisés).</t>
         </is>
@@ -7078,7 +7087,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>B - DÉCLARATION DE CONFORMITÉ AU SYSTÈME COMPTABLE DES ENTITÉS À BUT NON LUCRATIF ET FAITS MARQUANTS DE L'EXERCICE.</t>
         </is>
@@ -7087,7 +7096,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>C - RÈGLES, MÉTHODES COMPTABLES ET DÉROGATION AUX PRINCIPES COMPTABLES.</t>
         </is>
@@ -7096,7 +7105,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>D - INFORMATIONS COMPLÉMENTAIRES RELATIVES AU BILAN, AU COMPTE DE RÉSULTAT ET AU TABLEAU DES FLUX DE TRÉSORERIE.</t>
         </is>
@@ -7224,7 +7233,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Date d'arrêté des états financiers : </t>
         </is>
@@ -7233,7 +7242,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Organe ayant autorisé la publication des comptes : </t>
         </is>
@@ -7242,7 +7251,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>A - ÉVÈNEMENTS POSTÉRIEURS DONNANT LIEU À AJUSTEMENTS : nature des évènements et précisions sur les comptes ajustés.</t>
         </is>
@@ -7251,7 +7260,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>B - ÉVÈNEMENTS POSTÉRIEURS NE DONNANT PAS LIEU À AJUSTEMENTS : estimation de l'impact financier ou indication que l'estimation ne peut être fournie.</t>
         </is>
@@ -7260,7 +7269,7 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="122" t="inlineStr">
+      <c r="A21" s="123" t="inlineStr">
         <is>
           <t>C - ÉVÈNEMENTS REMETTANT EN CAUSE LA CONTINUITÉ DE L'EXPLOITATION : nature de l'évènement, valeurs liquidatives retenues.</t>
         </is>
@@ -7389,7 +7398,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>A - CHANGEMENTS DE MÉTHODES COMPTABLES : 1. changement de réglementation comptable ; 2. changement à l'initiative de l'entité (impact à l'ouverture, retraitement rétrospectif ou application prospective).</t>
         </is>
@@ -7398,7 +7407,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>B - CHANGEMENTS D'ESTIMATIONS : indiquer et justifier le changement d'estimation.</t>
         </is>
@@ -7407,7 +7416,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>C - CORRECTIONS D'ERREURS : nature des erreurs corrigées et principaux postes retraités.</t>
         </is>
@@ -7558,15 +7567,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -7598,15 +7607,15 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E11" s="120">
@@ -7621,15 +7630,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -7638,15 +7647,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="123" t="inlineStr">
+      <c r="A13" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B13" s="124" t="n"/>
-      <c r="C13" s="124" t="n"/>
-      <c r="D13" s="124" t="n"/>
-      <c r="E13" s="124" t="n"/>
+      <c r="B13" s="125" t="n"/>
+      <c r="C13" s="125" t="n"/>
+      <c r="D13" s="125" t="n"/>
+      <c r="E13" s="125" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="119" t="inlineStr">
@@ -7718,15 +7727,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="123" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
       </c>
-      <c r="B17" s="124" t="n"/>
-      <c r="C17" s="124" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="124" t="n"/>
+      <c r="B17" s="125" t="n"/>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="125" t="n"/>
+      <c r="E17" s="125" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="119" t="inlineStr">
@@ -7783,14 +7792,14 @@
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -7921,15 +7930,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -7938,15 +7947,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -8024,15 +8033,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="123" t="inlineStr">
+      <c r="A14" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B14" s="124" t="n"/>
-      <c r="C14" s="124" t="n"/>
-      <c r="D14" s="124" t="n"/>
-      <c r="E14" s="124" t="n"/>
+      <c r="B14" s="125" t="n"/>
+      <c r="C14" s="125" t="n"/>
+      <c r="D14" s="125" t="n"/>
+      <c r="E14" s="125" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="119" t="inlineStr">
@@ -8087,15 +8096,15 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E17" s="120">
@@ -8110,15 +8119,15 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E18" s="120">
@@ -8133,15 +8142,15 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E19" s="120">
@@ -8219,15 +8228,15 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="123" t="inlineStr">
+      <c r="A23" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
       </c>
-      <c r="B23" s="124" t="n"/>
-      <c r="C23" s="124" t="n"/>
-      <c r="D23" s="124" t="n"/>
-      <c r="E23" s="124" t="n"/>
+      <c r="B23" s="125" t="n"/>
+      <c r="C23" s="125" t="n"/>
+      <c r="D23" s="125" t="n"/>
+      <c r="E23" s="125" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="119" t="inlineStr">
@@ -8307,14 +8316,14 @@
       </c>
     </row>
     <row r="29"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="114">
-        <f>IF(SUM(B9:B26,C9:C26,D9:D26,E9:E26)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1"/>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="122">
+        <f>IF(SUM(B9:B26,C9:C26,D9:D26,E9:E26)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1"/>
+    <row r="32" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -9259,7 +9268,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="125" t="inlineStr">
+      <c r="A8" s="126" t="inlineStr">
         <is>
           <t>I : crédit-bail immobilier ; M : crédit-bail mobilier ; A : autres contrats</t>
         </is>
@@ -9345,15 +9354,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -9416,14 +9425,14 @@
       </c>
     </row>
     <row r="17"/>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="114">
-        <f>IF(SUM(B10:B14,C10:C14,D10:D14,E10:E14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1"/>
-    <row r="20" ht="26" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="122">
+        <f>IF(SUM(B10:B14,C10:C14,D10:D14,E10:E14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A8:E8"/>
@@ -9632,14 +9641,14 @@
       </c>
     </row>
     <row r="14"/>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="114">
-        <f>IF(SUM(B9:B11,C9:C11,D9:D11,E9:E11)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1"/>
-    <row r="17" ht="26" customHeight="1"/>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="122">
+        <f>IF(SUM(B9:B11,C9:C11,D9:D11,E9:E11)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A15:E17"/>
@@ -9770,15 +9779,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -9787,15 +9796,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -9850,15 +9859,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="123" t="inlineStr">
+      <c r="A13" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B13" s="124" t="n"/>
-      <c r="C13" s="124" t="n"/>
-      <c r="D13" s="124" t="n"/>
-      <c r="E13" s="124" t="n"/>
+      <c r="B13" s="125" t="n"/>
+      <c r="C13" s="125" t="n"/>
+      <c r="D13" s="125" t="n"/>
+      <c r="E13" s="125" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="119" t="inlineStr">
@@ -9890,15 +9899,15 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E15" s="120">
@@ -9913,15 +9922,15 @@
         </is>
       </c>
       <c r="B16" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E16" s="120">
@@ -10007,14 +10016,14 @@
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -10145,15 +10154,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -10179,15 +10188,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="123" t="inlineStr">
+      <c r="A11" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B11" s="124" t="n"/>
-      <c r="C11" s="124" t="n"/>
-      <c r="D11" s="124" t="n"/>
-      <c r="E11" s="124" t="n"/>
+      <c r="B11" s="125" t="n"/>
+      <c r="C11" s="125" t="n"/>
+      <c r="D11" s="125" t="n"/>
+      <c r="E11" s="125" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="119" t="inlineStr">
@@ -10305,15 +10314,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="123" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
       </c>
-      <c r="B17" s="124" t="n"/>
-      <c r="C17" s="124" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="124" t="n"/>
+      <c r="B17" s="125" t="n"/>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="125" t="n"/>
+      <c r="E17" s="125" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="119" t="inlineStr">
@@ -10393,14 +10402,14 @@
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B20,C9:C20,D9:D20,E9:E20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B20,C9:C20,D9:D20,E9:E20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -10657,14 +10666,14 @@
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="114">
-        <f>IF(SUM(B9:B13,C9:C13,D9:D13,E9:E13,F9:F13)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="122">
+        <f>IF(SUM(B9:B13,C9:C13,D9:D13,E9:E13,F9:F13)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A17:F19"/>
@@ -10772,7 +10781,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nature et date des réévaluations : </t>
         </is>
@@ -10781,7 +10790,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>Éléments réévalués par postes du bilan | Montants en coûts historiques | Montants réévalués | Écarts et provisions spéciales de réévaluation.</t>
         </is>
@@ -10790,7 +10799,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Méthode de réévaluation utilisée : </t>
         </is>
@@ -10799,7 +10808,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Traitement fiscal de l'écart de réévaluation et des amortissements supplémentaires : </t>
         </is>
@@ -10808,7 +10817,7 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="122" t="inlineStr">
+      <c r="A21" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Montant de l'écart incorporé à la dotation : </t>
         </is>
@@ -10999,7 +11008,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -11014,18 +11023,18 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"278*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"278*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"271*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"271*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"271*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"271*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"278*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"278*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"278*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"278*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"271*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"271*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"271*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"271*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"278*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"278*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D10" s="120">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -11051,7 +11060,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -11077,7 +11086,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -11103,7 +11112,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -11129,7 +11138,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -11155,7 +11164,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -11181,7 +11190,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -11207,7 +11216,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -11233,7 +11242,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -11255,7 +11264,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -11281,7 +11290,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="128">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -11298,21 +11307,21 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="122" t="inlineStr">
+      <c r="A23" s="123" t="inlineStr">
         <is>
           <t>• Justifier toute variation significative ; commenter les créances anciennes ; indiquer le nombre et la date d'acquisition des actions ou parts ; pour les dépréciations, indiquer les évènements et circonstances.</t>
         </is>
       </c>
     </row>
     <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="114">
-        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F16:F20,G16:G20,H16:H20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="122">
+        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F16:F20,G16:G20,H16:H20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -11447,15 +11456,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>ACTIF CIRCULANT HAO</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="128" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="129" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -11475,7 +11484,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -11498,7 +11507,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -11521,7 +11530,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="128">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -11544,7 +11553,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -11563,7 +11572,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -11586,7 +11595,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -11599,15 +11608,15 @@
       <c r="E16" s="119" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="123" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>DETTES CIRCULANTES HAO</t>
         </is>
       </c>
-      <c r="B17" s="124" t="n"/>
-      <c r="C17" s="124" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="128" t="n"/>
+      <c r="B17" s="125" t="n"/>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="125" t="n"/>
+      <c r="E17" s="129" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="119" t="inlineStr">
@@ -11627,7 +11636,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -11650,7 +11659,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -11673,7 +11682,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -11696,7 +11705,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -11719,7 +11728,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="127">
+      <c r="E22" s="128">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -11733,21 +11742,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative ; indiquer la date et la nature de l'immobilisation achetée et/ou cédée.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -11898,7 +11907,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -11921,7 +11930,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -11944,7 +11953,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -11967,7 +11976,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -11990,7 +11999,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -12013,7 +12022,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -12036,7 +12045,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -12059,7 +12068,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -12082,7 +12091,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -12101,7 +12110,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -12124,7 +12133,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -12138,21 +12147,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="122" t="inlineStr">
+      <c r="A22" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date de prise d'inventaire, la procédure et les méthodes d'évaluation ; commenter toute variation significative ; détailler les stocks dépréciés.</t>
         </is>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -12321,7 +12330,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -12347,7 +12356,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -12373,7 +12382,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -12399,7 +12408,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -12425,7 +12434,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -12451,7 +12460,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -12477,7 +12486,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -12499,7 +12508,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -12525,7 +12534,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -12561,7 +12570,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -12587,7 +12596,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -12613,7 +12622,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -12639,7 +12648,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="127">
+      <c r="E22" s="128">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -12656,21 +12665,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative et les créances anciennes ; indiquer les évènements motivant dépréciation et reprise.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F14:F22,G14:G22,H14:H22)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F14:F22,G14:G22,H14:H22)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -13051,7 +13060,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -13077,7 +13086,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -13103,7 +13112,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -13129,7 +13138,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -13155,7 +13164,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -13170,18 +13179,18 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -13196,18 +13205,18 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -13233,7 +13242,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -13248,18 +13257,18 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -13281,7 +13290,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -13307,7 +13316,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -13324,21 +13333,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="122" t="inlineStr">
+      <c r="A22" s="123" t="inlineStr">
         <is>
           <t>• Justifier toute variation significative ; détailler et justifier les créances significatives ou anciennes.</t>
         </is>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F16:F19,G16:G19,H16:H19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F16:F19,G16:G19,H16:H19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -13490,7 +13499,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -13513,7 +13522,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -13536,7 +13545,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -13559,7 +13568,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -13582,7 +13591,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -13605,7 +13614,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -13628,7 +13637,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -13651,7 +13660,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -13674,7 +13683,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -13693,7 +13702,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -13716,20 +13725,20 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
     </row>
     <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1"/>
-    <row r="23" ht="26" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -13880,7 +13889,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -13903,7 +13912,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -13926,7 +13935,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -13949,7 +13958,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -13972,7 +13981,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="127">
+      <c r="E13" s="128">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -13995,7 +14004,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -14014,7 +14023,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -14037,20 +14046,20 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
     </row>
     <row r="17"/>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="114">
-        <f>IF(SUM(B9:B16,C9:C16,D9:D16)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1"/>
-    <row r="20" ht="26" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="122">
+        <f>IF(SUM(B9:B16,C9:C16,D9:D16)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A18:E20"/>
@@ -14201,7 +14210,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -14224,7 +14233,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -14247,7 +14256,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -14259,18 +14268,18 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -14293,7 +14302,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -14316,7 +14325,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -14328,18 +14337,18 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -14362,7 +14371,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -14385,7 +14394,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -14408,7 +14417,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -14431,7 +14440,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -14443,18 +14452,18 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -14473,7 +14482,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="127">
+      <c r="E21" s="128">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -14496,7 +14505,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="127">
+      <c r="E22" s="128">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -14510,21 +14519,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date de rapprochement des comptes bancaires et la date d'inventaire de la caisse et des instruments de monnaie électronique. NB : les intérêts courus figurent ici en négatif si le compte principal attaché est débiteur.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -14675,7 +14684,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -14709,7 +14718,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -14734,21 +14743,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>• Détailler par devise : montant en devises, cours UML à l'année d'acquisition, cours UML au 31/12.</t>
         </is>
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="114">
-        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="122">
+        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A17:E19"/>
@@ -14888,18 +14897,18 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -14922,7 +14931,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -14945,7 +14954,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -14968,7 +14977,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="128">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -15025,14 +15034,14 @@
       <c r="E17" s="119" t="n"/>
     </row>
     <row r="18"/>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="114">
-        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1"/>
-    <row r="21" ht="26" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="122">
+        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -15183,7 +15192,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -15206,7 +15215,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -15229,7 +15238,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="127">
+      <c r="E11" s="128">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -15252,7 +15261,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -15266,21 +15275,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date des délibérations ou dispositions statutaires justifiant la variation des réserves et du report à nouveau.</t>
         </is>
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="114">
-        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="122">
+        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A17:E19"/>
@@ -15443,7 +15452,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -15468,7 +15477,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -15493,7 +15502,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -15518,7 +15527,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -15543,7 +15552,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -15568,7 +15577,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -15593,7 +15602,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -15618,7 +15627,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -15643,7 +15652,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -15668,7 +15677,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -15689,7 +15698,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -15714,7 +15723,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="128">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -15730,21 +15739,21 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="122" t="inlineStr">
+      <c r="A23" s="123" t="inlineStr">
         <is>
           <t>• Indiquer pour chaque subvention la date d'octroi, la nature, les obligations éventuelles ; pour les provisions réglementées, le texte de référence.</t>
         </is>
       </c>
     </row>
     <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="114">
-        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F17:F20,G17:G20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="122">
+        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F17:F20,G17:G20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A25:G27"/>
@@ -15885,18 +15894,18 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -15919,7 +15928,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -15942,7 +15951,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -15965,7 +15974,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -15988,7 +15997,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="127">
+      <c r="E13" s="128">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -16011,7 +16020,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -16034,7 +16043,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -16057,7 +16066,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -16080,7 +16089,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -16103,7 +16112,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -16117,21 +16126,21 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="122" t="inlineStr">
+      <c r="A21" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date d'affectation des fonds et leur mode de reprise ; la date des actes de donation et legs, la nature et la durée de jouissance de l'usufruit.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="114">
-        <f>IF(SUM(B9:B18,C9:C18,D9:D18)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="122">
+        <f>IF(SUM(B9:B18,C9:C18,D9:D18)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -16300,7 +16309,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -16326,7 +16335,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -16352,7 +16361,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -16378,7 +16387,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -16404,7 +16413,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -16430,7 +16439,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -16456,7 +16465,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -16482,7 +16491,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -16508,7 +16517,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -16534,7 +16543,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -16560,7 +16569,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -16575,18 +16584,18 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -16612,7 +16621,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="127">
+      <c r="E21" s="128">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -16638,7 +16647,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -16664,7 +16673,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -16690,7 +16699,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -16716,7 +16725,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="126">
+      <c r="E25" s="127">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -16742,7 +16751,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="126">
+      <c r="E26" s="127">
         <f>IF(C26=0,"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -16768,7 +16777,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="127">
+      <c r="E27" s="128">
         <f>IF(C27=0,"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -16794,7 +16803,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="128">
         <f>IF(C28=0,"",(B28-C28)/C28)</f>
         <v/>
       </c>
@@ -16811,21 +16820,21 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="122" t="inlineStr">
+      <c r="A31" s="123" t="inlineStr">
         <is>
           <t>• Pour chaque emprunt et dette de location-acquisition : date d'octroi, organisme, montant initial, durée, garanties données ; pour les pensions, méthode d'évaluation et descriptif de la convention.</t>
         </is>
       </c>
     </row>
     <row r="32"/>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="114">
-        <f>IF(SUM(B9:B28,C9:C28,D9:D28,F15:F28,G15:G28,H15:H28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1"/>
-    <row r="35" ht="26" customHeight="1"/>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="122">
+        <f>IF(SUM(B9:B28,C9:C28,D9:D28,F15:F28,G15:G28,H15:H28)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1"/>
+    <row r="35" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -17246,7 +17255,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>Actif éventuel (litiges, ...) : année N / année N-1.</t>
         </is>
@@ -17255,7 +17264,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>Passif éventuel (litiges, ...) : année N / année N-1.</t>
         </is>
@@ -17264,7 +17273,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>Décrire les principales caractéristiques, l'horizon des encaissements/décaissements attendus et les éventuels remboursements à percevoir.</t>
         </is>
@@ -17453,7 +17462,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -17479,7 +17488,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -17505,7 +17514,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -17531,7 +17540,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -17557,7 +17566,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -17583,7 +17592,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -17619,7 +17628,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -17645,7 +17654,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -17660,18 +17669,18 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4098*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4094*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4094*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4098*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4098*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4094*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4094*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4098*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D18" s="120">
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -17697,7 +17706,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -17706,14 +17715,14 @@
       <c r="H19" s="9" t="n"/>
     </row>
     <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F14:F19,G14:G19,H14:H19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1"/>
-    <row r="23" ht="26" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F14:F19,G14:G19,H14:H19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -17883,7 +17892,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -17909,7 +17918,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -17935,7 +17944,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -17950,18 +17959,18 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -17987,7 +17996,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -18013,7 +18022,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -18039,7 +18048,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -18065,7 +18074,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -18091,7 +18100,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -18117,7 +18126,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -18143,7 +18152,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -18158,18 +18167,18 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -18195,7 +18204,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -18221,7 +18230,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -18247,7 +18256,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="127">
+      <c r="E23" s="128">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -18273,7 +18282,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="127">
+      <c r="E24" s="128">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -18290,21 +18299,21 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="122" t="inlineStr">
+      <c r="A27" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative et les dettes anciennes.</t>
         </is>
       </c>
     </row>
     <row r="28"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="114">
-        <f>IF(SUM(B9:B24,C9:C24,D9:D24,F18:F24,G18:G24,H18:H24)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1"/>
-    <row r="31" ht="26" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="122">
+        <f>IF(SUM(B9:B24,C9:C24,D9:D24,F18:F24,G18:G24,H18:H24)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1"/>
+    <row r="31" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -18457,18 +18466,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>Fonds d'administration des projets</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="128" t="n"/>
-      <c r="F9" s="128" t="n"/>
-      <c r="G9" s="128" t="n"/>
-      <c r="H9" s="128" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="129" t="n"/>
+      <c r="F9" s="129" t="n"/>
+      <c r="G9" s="129" t="n"/>
+      <c r="H9" s="129" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -18488,7 +18497,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -18514,7 +18523,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -18540,7 +18549,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -18566,7 +18575,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="127">
+      <c r="E13" s="128">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -18581,18 +18590,18 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -18618,7 +18627,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -18644,7 +18653,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -18670,7 +18679,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -18696,7 +18705,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -18722,7 +18731,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -18748,7 +18757,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="128">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -18784,7 +18793,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -18801,21 +18810,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative et les dettes anciennes.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F13:F20,G13:G20,H13:H20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F13:F20,G13:G20,H13:H20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -18967,7 +18976,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -18990,7 +18999,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -19002,18 +19011,18 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D11" s="120">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -19025,18 +19034,18 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"526*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"566*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"566*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"526*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"526*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"566*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"566*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"526*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -19048,18 +19057,18 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"561*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"561*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"561*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"561*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -19082,7 +19091,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -19096,21 +19105,21 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="122" t="inlineStr">
+      <c r="A17" s="123" t="inlineStr">
         <is>
           <t>• Indiquer l'organisme, les conditions de crédit, le taux d'intérêt, la durée. NB : « Banques, intérêts courus » figure ici si le compte principal attaché est créditeur.</t>
         </is>
       </c>
     </row>
     <row r="18"/>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="114">
-        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1"/>
-    <row r="21" ht="26" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="122">
+        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -19261,7 +19270,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -19284,7 +19293,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -19307,7 +19316,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -19330,7 +19339,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -19353,7 +19362,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -19365,18 +19374,18 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -19399,7 +19408,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -19422,7 +19431,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -19434,18 +19443,18 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -19468,7 +19477,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -19491,7 +19500,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -19505,21 +19514,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="122" t="inlineStr">
+      <c r="A22" s="123" t="inlineStr">
         <is>
           <t>• Justifier toute variation significative ; détailler les revenus liés à la générosité (dons, legs, deniers du culte, zakat, célébrations, mécénat, parrainage).</t>
         </is>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -19670,7 +19679,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -19693,7 +19702,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="127">
+      <c r="E10" s="128">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -19716,7 +19725,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -19739,7 +19748,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="128">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -19762,7 +19771,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -19785,7 +19794,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -19808,7 +19817,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -19831,7 +19840,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -19854,7 +19863,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -19877,7 +19886,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -19900,20 +19909,20 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
     </row>
     <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1"/>
-    <row r="23" ht="26" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -20064,7 +20073,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -20087,7 +20096,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -20110,7 +20119,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -20133,7 +20142,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -20156,7 +20165,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -20179,20 +20188,20 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
     </row>
     <row r="15"/>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="114">
-        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1"/>
-    <row r="18" ht="26" customHeight="1"/>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="122">
+        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -20343,7 +20352,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -20366,7 +20375,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -20389,7 +20398,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -20412,7 +20421,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -20435,7 +20444,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -20458,7 +20467,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -20481,7 +20490,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -20504,7 +20513,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -20527,7 +20536,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -20550,7 +20559,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -20573,7 +20582,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -20596,7 +20605,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -20619,7 +20628,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -20642,7 +20651,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -20665,7 +20674,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -20688,7 +20697,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -20711,20 +20720,20 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="127">
+      <c r="E25" s="128">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B25,C9:C25,D9:D25)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B25,C9:C25,D9:D25)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -20875,7 +20884,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -20898,7 +20907,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -20921,7 +20930,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -20944,7 +20953,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -20967,7 +20976,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -20990,7 +20999,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -21013,7 +21022,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -21027,21 +21036,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>• Détailler pénalités et amendes et en indiquer la cause.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="114">
-        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="122">
+        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A20:E22"/>
@@ -21605,7 +21614,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -21628,7 +21637,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -21651,7 +21660,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -21674,7 +21683,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -21697,7 +21706,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -21720,7 +21729,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -21743,7 +21752,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -21757,21 +21766,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>• Indiquer les bénéficiaires des subventions versées.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="114">
-        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="122">
+        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A20:E22"/>
@@ -21922,7 +21931,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -21945,7 +21954,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -21968,7 +21977,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -21991,7 +22000,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -22014,7 +22023,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -22037,7 +22046,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -22060,7 +22069,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -22083,7 +22092,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -22106,7 +22115,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -22120,21 +22129,21 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="122" t="inlineStr">
+      <c r="A20" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la nature et la durée du contrat du personnel extérieur.</t>
         </is>
       </c>
     </row>
     <row r="21"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="114">
-        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1"/>
-    <row r="24" ht="26" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="122">
+        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A22:E24"/>
@@ -22468,14 +22477,14 @@
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B24:B24,F10:F14,G10:G14,H10:H14,I10:I14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B24:B24,F10:F14,G10:G14,H10:H14,I10:I14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:F4"/>
@@ -22869,17 +22878,17 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="120" t="n"/>
       <c r="F17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="G17" s="120" t="n"/>
@@ -23219,14 +23228,14 @@
       </c>
     </row>
     <row r="31"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="114">
-        <f>IF(SUM(B9:B28,C9:C28,D9:D28,E9:E28,F9:F28,G9:G28,H9:H28,I9:I28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1"/>
-    <row r="34" ht="26" customHeight="1"/>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="122">
+        <f>IF(SUM(B9:B28,C9:C28,D9:D28,E9:E28,F9:F28,G9:G28,H9:H28,I9:I28)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1"/>
+    <row r="34" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:F4"/>
@@ -23378,7 +23387,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -23401,7 +23410,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -23424,7 +23433,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -23447,7 +23456,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -23470,7 +23479,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -23493,7 +23502,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -23516,7 +23525,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -23539,7 +23548,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -23562,7 +23571,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -23585,7 +23594,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -23608,7 +23617,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -23631,7 +23640,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -23654,7 +23663,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -23677,7 +23686,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -23700,7 +23709,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -23723,7 +23732,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -23746,7 +23755,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="126">
+      <c r="E25" s="127">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -23769,7 +23778,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="126">
+      <c r="E26" s="127">
         <f>IF(C26=0,"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -23792,7 +23801,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="127">
+      <c r="E27" s="128">
         <f>IF(C27=0,"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -23815,20 +23824,20 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="128">
         <f>IF(C28=0,"",(B28-C28)/C28)</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="114">
-        <f>IF(SUM(B9:B28,C9:C28,D9:D28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1"/>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="122">
+        <f>IF(SUM(B9:B28,C9:C28,D9:D28)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1"/>
+    <row r="32" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -23979,7 +23988,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -24002,7 +24011,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -24025,7 +24034,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -24048,7 +24057,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -24071,7 +24080,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -24094,7 +24103,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -24117,7 +24126,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -24140,7 +24149,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -24163,7 +24172,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -24186,7 +24195,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -24209,7 +24218,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -24232,7 +24241,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -24255,7 +24264,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -24278,7 +24287,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -24301,7 +24310,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -24324,7 +24333,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -24347,7 +24356,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="126">
+      <c r="E25" s="127">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -24370,7 +24379,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="126">
+      <c r="E26" s="127">
         <f>IF(C26=0,"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -24393,7 +24402,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="126">
+      <c r="E27" s="127">
         <f>IF(C27=0,"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -24416,7 +24425,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="128">
         <f>IF(C28=0,"",(B28-C28)/C28)</f>
         <v/>
       </c>
@@ -24439,20 +24448,20 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="127">
+      <c r="E29" s="128">
         <f>IF(C29=0,"",(B29-C29)/C29)</f>
         <v/>
       </c>
     </row>
     <row r="30"/>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="114">
-        <f>IF(SUM(B9:B29,C9:C29,D9:D29)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1"/>
-    <row r="33" ht="26" customHeight="1"/>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="122">
+        <f>IF(SUM(B9:B29,C9:C29,D9:D29)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1"/>
+    <row r="33" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -24556,42 +24565,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="129" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>(en unités monétaires légales)</t>
         </is>
       </c>
-      <c r="B8" s="130" t="inlineStr">
+      <c r="B8" s="131" t="inlineStr">
         <is>
           <t>Année N</t>
         </is>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Année N-1</t>
         </is>
       </c>
-      <c r="D8" s="130" t="inlineStr">
+      <c r="D8" s="131" t="inlineStr">
         <is>
           <t>Variation en valeur</t>
         </is>
       </c>
-      <c r="E8" s="129" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Variation en %</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE L'ACTIVITÉ - SOLDES INTERMÉDIAIRES DE GESTION</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="128" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="129" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -24611,7 +24620,7 @@
         <f>IF(OR(B10="",C10=""),"",B10-C10)</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(OR(C10="",C10=0),"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -24634,7 +24643,7 @@
         <f>IF(OR(B11="",C11=""),"",B11-C11)</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(OR(C11="",C11=0),"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -24657,7 +24666,7 @@
         <f>IF(OR(B12="",C12=""),"",B12-C12)</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(OR(C12="",C12=0),"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -24669,18 +24678,18 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
         <f>IF(OR(B13="",C13=""),"",B13-C13)</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(OR(C13="",C13=0),"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -24703,7 +24712,7 @@
         <f>IF(OR(B14="",C14=""),"",B14-C14)</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(OR(C14="",C14=0),"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -24720,15 +24729,15 @@
       <c r="E15" s="119" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="123" t="inlineStr">
+      <c r="A16" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE LA STRUCTURE FINANCIÈRE</t>
         </is>
       </c>
-      <c r="B16" s="124" t="n"/>
-      <c r="C16" s="124" t="n"/>
-      <c r="D16" s="124" t="n"/>
-      <c r="E16" s="128" t="n"/>
+      <c r="B16" s="125" t="n"/>
+      <c r="C16" s="125" t="n"/>
+      <c r="D16" s="125" t="n"/>
+      <c r="E16" s="129" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="119" t="inlineStr">
@@ -24748,7 +24757,7 @@
         <f>IF(OR(B17="",C17=""),"",B17-C17)</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(OR(C17="",C17=0),"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -24771,7 +24780,7 @@
         <f>IF(OR(B18="",C18=""),"",B18-C18)</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(OR(C18="",C18=0),"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -24794,7 +24803,7 @@
         <f>IF(OR(B19="",C19=""),"",B19-C19)</f>
         <v/>
       </c>
-      <c r="E19" s="131">
+      <c r="E19" s="132">
         <f>IF(OR(C19="",C19=0),"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -24817,7 +24826,7 @@
         <f>IF(OR(B20="",C20=""),"",B20-C20)</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(OR(C20="",C20=0),"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -24840,7 +24849,7 @@
         <f>IF(OR(B21="",C21=""),"",B21-C21)</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(OR(C21="",C21=0),"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -24863,7 +24872,7 @@
         <f>IF(OR(B22="",C22=""),"",B22-C22)</f>
         <v/>
       </c>
-      <c r="E22" s="131">
+      <c r="E22" s="132">
         <f>IF(OR(C22="",C22=0),"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -24886,7 +24895,7 @@
         <f>IF(OR(B23="",C23=""),"",B23-C23)</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(OR(C23="",C23=0),"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -24909,7 +24918,7 @@
         <f>IF(OR(B24="",C24=""),"",B24-C24)</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(OR(C24="",C24=0),"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -24932,7 +24941,7 @@
         <f>IF(OR(B25="",C25=""),"",B25-C25)</f>
         <v/>
       </c>
-      <c r="E25" s="131">
+      <c r="E25" s="132">
         <f>IF(OR(C25="",C25=0),"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -24955,7 +24964,7 @@
         <f>IF(OR(B26="",C26=""),"",B26-C26)</f>
         <v/>
       </c>
-      <c r="E26" s="131">
+      <c r="E26" s="132">
         <f>IF(OR(C26="",C26=0),"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -24978,7 +24987,7 @@
         <f>IF(OR(B27="",C27=""),"",B27-C27)</f>
         <v/>
       </c>
-      <c r="E27" s="131">
+      <c r="E27" s="132">
         <f>IF(OR(C27="",C27=0),"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -25001,21 +25010,21 @@
         <f>IF(OR(B28="",C28=""),"",B28-C28)</f>
         <v/>
       </c>
-      <c r="E28" s="126">
+      <c r="E28" s="127">
         <f>IF(OR(C28="",C28=0),"",(B28-C28)/C28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="123" t="inlineStr">
+      <c r="A29" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE LA SOLVABILITÉ</t>
         </is>
       </c>
-      <c r="B29" s="124" t="n"/>
-      <c r="C29" s="124" t="n"/>
-      <c r="D29" s="124" t="n"/>
-      <c r="E29" s="128" t="n"/>
+      <c r="B29" s="125" t="n"/>
+      <c r="C29" s="125" t="n"/>
+      <c r="D29" s="125" t="n"/>
+      <c r="E29" s="129" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="119" t="inlineStr">
@@ -25035,21 +25044,21 @@
         <f>IF(OR(B30="",C30=""),"",B30-C30)</f>
         <v/>
       </c>
-      <c r="E30" s="126">
+      <c r="E30" s="127">
         <f>IF(OR(C30="",C30=0),"",(B30-C30)/C30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="123" t="inlineStr">
+      <c r="A31" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE LA VARIATION DE LA TRÉSORERIE</t>
         </is>
       </c>
-      <c r="B31" s="124" t="n"/>
-      <c r="C31" s="124" t="n"/>
-      <c r="D31" s="124" t="n"/>
-      <c r="E31" s="128" t="n"/>
+      <c r="B31" s="125" t="n"/>
+      <c r="C31" s="125" t="n"/>
+      <c r="D31" s="125" t="n"/>
+      <c r="E31" s="129" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="119" t="inlineStr">
@@ -25069,7 +25078,7 @@
         <f>IF(OR(B32="",C32=""),"",B32-C32)</f>
         <v/>
       </c>
-      <c r="E32" s="126">
+      <c r="E32" s="127">
         <f>IF(OR(C32="",C32=0),"",(B32-C32)/C32)</f>
         <v/>
       </c>
@@ -25092,7 +25101,7 @@
         <f>IF(OR(B33="",C33=""),"",B33-C33)</f>
         <v/>
       </c>
-      <c r="E33" s="126">
+      <c r="E33" s="127">
         <f>IF(OR(C33="",C33=0),"",(B33-C33)/C33)</f>
         <v/>
       </c>
@@ -25115,7 +25124,7 @@
         <f>IF(OR(B34="",C34=""),"",B34-C34)</f>
         <v/>
       </c>
-      <c r="E34" s="126">
+      <c r="E34" s="127">
         <f>IF(OR(C34="",C34=0),"",(B34-C34)/C34)</f>
         <v/>
       </c>
@@ -25138,7 +25147,7 @@
         <f>IF(OR(B35="",C35=""),"",B35-C35)</f>
         <v/>
       </c>
-      <c r="E35" s="126">
+      <c r="E35" s="127">
         <f>IF(OR(C35="",C35=0),"",(B35-C35)/C35)</f>
         <v/>
       </c>
@@ -25152,14 +25161,14 @@
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="114">
-        <f>IF(SUM(B8:B35,C8:C35,D8:D35)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="26" customHeight="1"/>
-    <row r="41" ht="26" customHeight="1"/>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="122">
+        <f>IF(SUM(B8:B35,C8:C35,D8:D35)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1"/>
+    <row r="41" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A39:E41"/>
@@ -25266,7 +25275,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>(Note obligatoire pour les entités de plus de 250 personnes, bénévoles compris.)</t>
         </is>
@@ -25275,7 +25284,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>INFORMATIONS SOCIALES : emploi (effectif total, répartition par sexe, âge et zone géographique ; embauches et licenciements ; rémunérations et leur évolution) ; relations sociales ; santé et sécurité ; formation ; égalité de traitement.</t>
         </is>
@@ -25284,7 +25293,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>INFORMATIONS ENVIRONNEMENTALES : politique générale ; pollution et gestion des déchets ; utilisation durable des ressources ; changement climatique ; protection de la biodiversité.</t>
         </is>
@@ -25293,7 +25302,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>ENGAGEMENTS SOCIÉTAUX EN FAVEUR DU DÉVELOPPEMENT DURABLE : impact territorial, économique et social ; relations avec les parties prenantes ; sous-traitance et fournisseurs.</t>
         </is>
@@ -25479,7 +25488,7 @@
         <f>C9-F9</f>
         <v/>
       </c>
-      <c r="H9" s="126">
+      <c r="H9" s="127">
         <f>IF(C9=0,"",F9/C9)</f>
         <v/>
       </c>
@@ -25498,7 +25507,7 @@
         <f>C10-F10</f>
         <v/>
       </c>
-      <c r="H10" s="126">
+      <c r="H10" s="127">
         <f>IF(C10=0,"",F10/C10)</f>
         <v/>
       </c>
@@ -25517,7 +25526,7 @@
         <f>C11-F11</f>
         <v/>
       </c>
-      <c r="H11" s="126">
+      <c r="H11" s="127">
         <f>IF(C11=0,"",F11/C11)</f>
         <v/>
       </c>
@@ -25536,7 +25545,7 @@
         <f>C12-F12</f>
         <v/>
       </c>
-      <c r="H12" s="126">
+      <c r="H12" s="127">
         <f>IF(C12=0,"",F12/C12)</f>
         <v/>
       </c>
@@ -25555,7 +25564,7 @@
         <f>C13-F13</f>
         <v/>
       </c>
-      <c r="H13" s="126">
+      <c r="H13" s="127">
         <f>IF(C13=0,"",F13/C13)</f>
         <v/>
       </c>
@@ -25574,7 +25583,7 @@
         <f>C14-F14</f>
         <v/>
       </c>
-      <c r="H14" s="126">
+      <c r="H14" s="127">
         <f>IF(C14=0,"",F14/C14)</f>
         <v/>
       </c>
@@ -25593,7 +25602,7 @@
         <f>C15-F15</f>
         <v/>
       </c>
-      <c r="H15" s="126">
+      <c r="H15" s="127">
         <f>IF(C15=0,"",F15/C15)</f>
         <v/>
       </c>
@@ -25612,7 +25621,7 @@
         <f>C16-F16</f>
         <v/>
       </c>
-      <c r="H16" s="126">
+      <c r="H16" s="127">
         <f>IF(C16=0,"",F16/C16)</f>
         <v/>
       </c>
@@ -25631,7 +25640,7 @@
         <f>C17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="126">
+      <c r="H17" s="127">
         <f>IF(C17=0,"",F17/C17)</f>
         <v/>
       </c>
@@ -25650,7 +25659,7 @@
         <f>C18-F18</f>
         <v/>
       </c>
-      <c r="H18" s="126">
+      <c r="H18" s="127">
         <f>IF(C18=0,"",F18/C18)</f>
         <v/>
       </c>
@@ -25669,7 +25678,7 @@
         <f>C19-F19</f>
         <v/>
       </c>
-      <c r="H19" s="126">
+      <c r="H19" s="127">
         <f>IF(C19=0,"",F19/C19)</f>
         <v/>
       </c>
@@ -25688,7 +25697,7 @@
         <f>C20-F20</f>
         <v/>
       </c>
-      <c r="H20" s="126">
+      <c r="H20" s="127">
         <f>IF(C20=0,"",F20/C20)</f>
         <v/>
       </c>
@@ -25720,7 +25729,7 @@
         <f>SUM(G9:G20)</f>
         <v/>
       </c>
-      <c r="H21" s="131">
+      <c r="H21" s="132">
         <f>IF(C21=0,"",F21/C21)</f>
         <v/>
       </c>
@@ -25734,14 +25743,14 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="114">
-        <f>IF(SUM(C9:C21,D9:D21,E9:E21,F9:F21,G9:G21)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="122">
+        <f>IF(SUM(C9:C21,D9:D21,E9:E21,F9:F21,G9:G21)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -25778,7 +25787,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G1" s="132" t="inlineStr">
+      <c r="G1" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 1/12</t>
@@ -25830,26 +25839,26 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="133" t="inlineStr">
+      <c r="A6" s="134" t="inlineStr">
         <is>
           <t>Partie 1 : Informations générales</t>
         </is>
       </c>
-      <c r="B6" s="134" t="n"/>
-      <c r="C6" s="134" t="n"/>
-      <c r="D6" s="134" t="n"/>
-      <c r="E6" s="134" t="n"/>
-      <c r="F6" s="134" t="n"/>
-      <c r="G6" s="134" t="n"/>
-      <c r="H6" s="134" t="n"/>
+      <c r="B6" s="135" t="n"/>
+      <c r="C6" s="135" t="n"/>
+      <c r="D6" s="135" t="n"/>
+      <c r="E6" s="135" t="n"/>
+      <c r="F6" s="135" t="n"/>
+      <c r="G6" s="135" t="n"/>
+      <c r="H6" s="135" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="135" t="inlineStr">
+      <c r="A7" s="136" t="inlineStr">
         <is>
           <t>Note 1</t>
         </is>
       </c>
-      <c r="B7" s="136" t="inlineStr">
+      <c r="B7" s="137" t="inlineStr">
         <is>
           <t>DETTES GARANTIES PAR DES SÛRETÉS RÉELLES, ENGAGEMENTS FINANCIERS ET CONTRIBUTIONS VOLONTAIRES EN NATURE</t>
         </is>
@@ -25862,7 +25871,7 @@
       <c r="H7" s="49" t="n"/>
     </row>
     <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="137" t="n"/>
+      <c r="A8" s="138" t="n"/>
       <c r="B8" s="49" t="n"/>
       <c r="C8" s="49" t="n"/>
       <c r="D8" s="49" t="n"/>
@@ -25872,12 +25881,12 @@
       <c r="H8" s="49" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="135" t="inlineStr">
+      <c r="A9" s="136" t="inlineStr">
         <is>
           <t>Note 2</t>
         </is>
       </c>
-      <c r="B9" s="136" t="inlineStr">
+      <c r="B9" s="137" t="inlineStr">
         <is>
           <t>INFORMATIONS OBLIGATOIRES</t>
         </is>
@@ -25890,7 +25899,7 @@
       <c r="H9" s="49" t="n"/>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="137" t="n"/>
+      <c r="A10" s="138" t="n"/>
       <c r="B10" s="49" t="n"/>
       <c r="C10" s="49" t="n"/>
       <c r="D10" s="49" t="n"/>
@@ -25900,12 +25909,12 @@
       <c r="H10" s="49" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="135" t="inlineStr">
+      <c r="A11" s="136" t="inlineStr">
         <is>
           <t>Note 3</t>
         </is>
       </c>
-      <c r="B11" s="136" t="inlineStr">
+      <c r="B11" s="137" t="inlineStr">
         <is>
           <t>ÉVÈNEMENTS POSTÉRIEURS À LA CLÔTURE DE L'EXERCICE</t>
         </is>
@@ -25918,7 +25927,7 @@
       <c r="H11" s="49" t="n"/>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="137" t="n"/>
+      <c r="A12" s="138" t="n"/>
       <c r="B12" s="49" t="n"/>
       <c r="C12" s="49" t="n"/>
       <c r="D12" s="49" t="n"/>
@@ -25928,12 +25937,12 @@
       <c r="H12" s="49" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="135" t="inlineStr">
+      <c r="A13" s="136" t="inlineStr">
         <is>
           <t>Note 4</t>
         </is>
       </c>
-      <c r="B13" s="136" t="inlineStr">
+      <c r="B13" s="137" t="inlineStr">
         <is>
           <t>CHANGEMENTS DE MÉTHODES COMPTABLES, D'ESTIMATIONS ET CORRECTIONS D'ERREURS</t>
         </is>
@@ -25946,7 +25955,7 @@
       <c r="H13" s="49" t="n"/>
     </row>
     <row r="14" ht="110" customHeight="1">
-      <c r="A14" s="137" t="n"/>
+      <c r="A14" s="138" t="n"/>
       <c r="B14" s="49" t="n"/>
       <c r="C14" s="49" t="n"/>
       <c r="D14" s="49" t="n"/>
@@ -25961,7 +25970,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G15" s="132" t="inlineStr">
+      <c r="G15" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 2/12</t>
@@ -26013,26 +26022,26 @@
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="133" t="inlineStr">
+      <c r="A20" s="134" t="inlineStr">
         <is>
           <t>Partie 2 : Notes sur le bilan</t>
         </is>
       </c>
-      <c r="B20" s="134" t="n"/>
-      <c r="C20" s="134" t="n"/>
-      <c r="D20" s="134" t="n"/>
-      <c r="E20" s="134" t="n"/>
-      <c r="F20" s="134" t="n"/>
-      <c r="G20" s="134" t="n"/>
-      <c r="H20" s="134" t="n"/>
+      <c r="B20" s="135" t="n"/>
+      <c r="C20" s="135" t="n"/>
+      <c r="D20" s="135" t="n"/>
+      <c r="E20" s="135" t="n"/>
+      <c r="F20" s="135" t="n"/>
+      <c r="G20" s="135" t="n"/>
+      <c r="H20" s="135" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="135" t="inlineStr">
+      <c r="A21" s="136" t="inlineStr">
         <is>
           <t>Note 5A</t>
         </is>
       </c>
-      <c r="B21" s="136" t="inlineStr">
+      <c r="B21" s="137" t="inlineStr">
         <is>
           <t>DONS ET LEGS D'IMMOBILISATIONS NON REÇUS DESTINÉS À LA VENTE ET USUFRUIT TEMPORAIRE</t>
         </is>
@@ -26045,7 +26054,7 @@
       <c r="H21" s="49" t="n"/>
     </row>
     <row r="22" ht="110" customHeight="1">
-      <c r="A22" s="137" t="n"/>
+      <c r="A22" s="138" t="n"/>
       <c r="B22" s="49" t="n"/>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
@@ -26055,12 +26064,12 @@
       <c r="H22" s="49" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="135" t="inlineStr">
+      <c r="A23" s="136" t="inlineStr">
         <is>
           <t>Note 5B</t>
         </is>
       </c>
-      <c r="B23" s="136" t="inlineStr">
+      <c r="B23" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS BRUTES</t>
         </is>
@@ -26073,7 +26082,7 @@
       <c r="H23" s="49" t="n"/>
     </row>
     <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="137" t="n"/>
+      <c r="A24" s="138" t="n"/>
       <c r="B24" s="49" t="n"/>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
@@ -26083,12 +26092,12 @@
       <c r="H24" s="49" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="135" t="inlineStr">
+      <c r="A25" s="136" t="inlineStr">
         <is>
           <t>Note 5C</t>
         </is>
       </c>
-      <c r="B25" s="136" t="inlineStr">
+      <c r="B25" s="137" t="inlineStr">
         <is>
           <t>BIENS PRIS EN LOCATION-ACQUISITION</t>
         </is>
@@ -26101,7 +26110,7 @@
       <c r="H25" s="49" t="n"/>
     </row>
     <row r="26" ht="110" customHeight="1">
-      <c r="A26" s="137" t="n"/>
+      <c r="A26" s="138" t="n"/>
       <c r="B26" s="49" t="n"/>
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
@@ -26111,12 +26120,12 @@
       <c r="H26" s="49" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="135" t="inlineStr">
+      <c r="A27" s="136" t="inlineStr">
         <is>
           <t>Note 5D</t>
         </is>
       </c>
-      <c r="B27" s="136" t="inlineStr">
+      <c r="B27" s="137" t="inlineStr">
         <is>
           <t>DONS ET LEGS D'IMMOBILISATIONS NON REÇUS DESTINÉS À LA VENTE ET USUFRUIT TEMPORAIRE (AMORTISSEMENTS ET DÉPRÉCIATIONS)</t>
         </is>
@@ -26129,7 +26138,7 @@
       <c r="H27" s="49" t="n"/>
     </row>
     <row r="28" ht="110" customHeight="1">
-      <c r="A28" s="137" t="n"/>
+      <c r="A28" s="138" t="n"/>
       <c r="B28" s="49" t="n"/>
       <c r="C28" s="49" t="n"/>
       <c r="D28" s="49" t="n"/>
@@ -26144,7 +26153,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G29" s="132" t="inlineStr">
+      <c r="G29" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 3/12</t>
@@ -26196,12 +26205,12 @@
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="135" t="inlineStr">
+      <c r="A34" s="136" t="inlineStr">
         <is>
           <t>Note 5E</t>
         </is>
       </c>
-      <c r="B34" s="136" t="inlineStr">
+      <c r="B34" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS : AMORTISSEMENTS</t>
         </is>
@@ -26214,7 +26223,7 @@
       <c r="H34" s="49" t="n"/>
     </row>
     <row r="35" ht="110" customHeight="1">
-      <c r="A35" s="137" t="n"/>
+      <c r="A35" s="138" t="n"/>
       <c r="B35" s="49" t="n"/>
       <c r="C35" s="49" t="n"/>
       <c r="D35" s="49" t="n"/>
@@ -26224,12 +26233,12 @@
       <c r="H35" s="49" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="135" t="inlineStr">
+      <c r="A36" s="136" t="inlineStr">
         <is>
           <t>Note 5F</t>
         </is>
       </c>
-      <c r="B36" s="136" t="inlineStr">
+      <c r="B36" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS : DÉPRÉCIATIONS</t>
         </is>
@@ -26242,7 +26251,7 @@
       <c r="H36" s="49" t="n"/>
     </row>
     <row r="37" ht="110" customHeight="1">
-      <c r="A37" s="137" t="n"/>
+      <c r="A37" s="138" t="n"/>
       <c r="B37" s="49" t="n"/>
       <c r="C37" s="49" t="n"/>
       <c r="D37" s="49" t="n"/>
@@ -26252,12 +26261,12 @@
       <c r="H37" s="49" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="135" t="inlineStr">
+      <c r="A38" s="136" t="inlineStr">
         <is>
           <t>Note 5G</t>
         </is>
       </c>
-      <c r="B38" s="136" t="inlineStr">
+      <c r="B38" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS : PLUS-VALUES ET MOINS-VALUES DE CESSION</t>
         </is>
@@ -26270,7 +26279,7 @@
       <c r="H38" s="49" t="n"/>
     </row>
     <row r="39" ht="110" customHeight="1">
-      <c r="A39" s="137" t="n"/>
+      <c r="A39" s="138" t="n"/>
       <c r="B39" s="49" t="n"/>
       <c r="C39" s="49" t="n"/>
       <c r="D39" s="49" t="n"/>
@@ -26280,12 +26289,12 @@
       <c r="H39" s="49" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="135" t="inlineStr">
+      <c r="A40" s="136" t="inlineStr">
         <is>
           <t>Note 5H</t>
         </is>
       </c>
-      <c r="B40" s="136" t="inlineStr">
+      <c r="B40" s="137" t="inlineStr">
         <is>
           <t>INFORMATIONS SUR LES RÉÉVALUATIONS EFFECTUÉES PAR L'ENTITÉ</t>
         </is>
@@ -26298,7 +26307,7 @@
       <c r="H40" s="49" t="n"/>
     </row>
     <row r="41" ht="110" customHeight="1">
-      <c r="A41" s="137" t="n"/>
+      <c r="A41" s="138" t="n"/>
       <c r="B41" s="49" t="n"/>
       <c r="C41" s="49" t="n"/>
       <c r="D41" s="49" t="n"/>
@@ -26313,7 +26322,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G42" s="132" t="inlineStr">
+      <c r="G42" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 4/12</t>
@@ -26365,12 +26374,12 @@
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="135" t="inlineStr">
+      <c r="A47" s="136" t="inlineStr">
         <is>
           <t>Note 6</t>
         </is>
       </c>
-      <c r="B47" s="136" t="inlineStr">
+      <c r="B47" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
@@ -26383,7 +26392,7 @@
       <c r="H47" s="49" t="n"/>
     </row>
     <row r="48" ht="110" customHeight="1">
-      <c r="A48" s="137" t="n"/>
+      <c r="A48" s="138" t="n"/>
       <c r="B48" s="49" t="n"/>
       <c r="C48" s="49" t="n"/>
       <c r="D48" s="49" t="n"/>
@@ -26393,12 +26402,12 @@
       <c r="H48" s="49" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="135" t="inlineStr">
+      <c r="A49" s="136" t="inlineStr">
         <is>
           <t>Note 7</t>
         </is>
       </c>
-      <c r="B49" s="136" t="inlineStr">
+      <c r="B49" s="137" t="inlineStr">
         <is>
           <t>ACTIF CIRCULANT ET DETTES CIRCULANTES HAO</t>
         </is>
@@ -26411,7 +26420,7 @@
       <c r="H49" s="49" t="n"/>
     </row>
     <row r="50" ht="110" customHeight="1">
-      <c r="A50" s="137" t="n"/>
+      <c r="A50" s="138" t="n"/>
       <c r="B50" s="49" t="n"/>
       <c r="C50" s="49" t="n"/>
       <c r="D50" s="49" t="n"/>
@@ -26421,12 +26430,12 @@
       <c r="H50" s="49" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="135" t="inlineStr">
+      <c r="A51" s="136" t="inlineStr">
         <is>
           <t>Note 8</t>
         </is>
       </c>
-      <c r="B51" s="136" t="inlineStr">
+      <c r="B51" s="137" t="inlineStr">
         <is>
           <t>STOCKS ET ENCOURS</t>
         </is>
@@ -26439,7 +26448,7 @@
       <c r="H51" s="49" t="n"/>
     </row>
     <row r="52" ht="110" customHeight="1">
-      <c r="A52" s="137" t="n"/>
+      <c r="A52" s="138" t="n"/>
       <c r="B52" s="49" t="n"/>
       <c r="C52" s="49" t="n"/>
       <c r="D52" s="49" t="n"/>
@@ -26449,12 +26458,12 @@
       <c r="H52" s="49" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="135" t="inlineStr">
+      <c r="A53" s="136" t="inlineStr">
         <is>
           <t>Note 9</t>
         </is>
       </c>
-      <c r="B53" s="136" t="inlineStr">
+      <c r="B53" s="137" t="inlineStr">
         <is>
           <t>ADHÉRENTS, CLIENTS-USAGERS</t>
         </is>
@@ -26467,7 +26476,7 @@
       <c r="H53" s="49" t="n"/>
     </row>
     <row r="54" ht="110" customHeight="1">
-      <c r="A54" s="137" t="n"/>
+      <c r="A54" s="138" t="n"/>
       <c r="B54" s="49" t="n"/>
       <c r="C54" s="49" t="n"/>
       <c r="D54" s="49" t="n"/>
@@ -26482,7 +26491,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G55" s="132" t="inlineStr">
+      <c r="G55" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 5/12</t>
@@ -26534,12 +26543,12 @@
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="135" t="inlineStr">
+      <c r="A60" s="136" t="inlineStr">
         <is>
           <t>Note 10</t>
         </is>
       </c>
-      <c r="B60" s="136" t="inlineStr">
+      <c r="B60" s="137" t="inlineStr">
         <is>
           <t>AUTRES CRÉANCES</t>
         </is>
@@ -26552,7 +26561,7 @@
       <c r="H60" s="49" t="n"/>
     </row>
     <row r="61" ht="110" customHeight="1">
-      <c r="A61" s="137" t="n"/>
+      <c r="A61" s="138" t="n"/>
       <c r="B61" s="49" t="n"/>
       <c r="C61" s="49" t="n"/>
       <c r="D61" s="49" t="n"/>
@@ -26562,12 +26571,12 @@
       <c r="H61" s="49" t="n"/>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="135" t="inlineStr">
+      <c r="A62" s="136" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
       </c>
-      <c r="B62" s="136" t="inlineStr">
+      <c r="B62" s="137" t="inlineStr">
         <is>
           <t>TITRES DE PLACEMENT</t>
         </is>
@@ -26580,7 +26589,7 @@
       <c r="H62" s="49" t="n"/>
     </row>
     <row r="63" ht="110" customHeight="1">
-      <c r="A63" s="137" t="n"/>
+      <c r="A63" s="138" t="n"/>
       <c r="B63" s="49" t="n"/>
       <c r="C63" s="49" t="n"/>
       <c r="D63" s="49" t="n"/>
@@ -26590,12 +26599,12 @@
       <c r="H63" s="49" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="135" t="inlineStr">
+      <c r="A64" s="136" t="inlineStr">
         <is>
           <t>Note 12</t>
         </is>
       </c>
-      <c r="B64" s="136" t="inlineStr">
+      <c r="B64" s="137" t="inlineStr">
         <is>
           <t>VALEURS À ENCAISSER</t>
         </is>
@@ -26608,7 +26617,7 @@
       <c r="H64" s="49" t="n"/>
     </row>
     <row r="65" ht="110" customHeight="1">
-      <c r="A65" s="137" t="n"/>
+      <c r="A65" s="138" t="n"/>
       <c r="B65" s="49" t="n"/>
       <c r="C65" s="49" t="n"/>
       <c r="D65" s="49" t="n"/>
@@ -26618,12 +26627,12 @@
       <c r="H65" s="49" t="n"/>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="135" t="inlineStr">
+      <c r="A66" s="136" t="inlineStr">
         <is>
           <t>Note 13</t>
         </is>
       </c>
-      <c r="B66" s="136" t="inlineStr">
+      <c r="B66" s="137" t="inlineStr">
         <is>
           <t>DISPONIBILITÉS</t>
         </is>
@@ -26636,7 +26645,7 @@
       <c r="H66" s="49" t="n"/>
     </row>
     <row r="67" ht="110" customHeight="1">
-      <c r="A67" s="137" t="n"/>
+      <c r="A67" s="138" t="n"/>
       <c r="B67" s="49" t="n"/>
       <c r="C67" s="49" t="n"/>
       <c r="D67" s="49" t="n"/>
@@ -26651,7 +26660,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G68" s="132" t="inlineStr">
+      <c r="G68" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 6/12</t>
@@ -26703,12 +26712,12 @@
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="135" t="inlineStr">
+      <c r="A73" s="136" t="inlineStr">
         <is>
           <t>Note 14</t>
         </is>
       </c>
-      <c r="B73" s="136" t="inlineStr">
+      <c r="B73" s="137" t="inlineStr">
         <is>
           <t>ÉCARTS DE CONVERSION</t>
         </is>
@@ -26721,7 +26730,7 @@
       <c r="H73" s="49" t="n"/>
     </row>
     <row r="74" ht="110" customHeight="1">
-      <c r="A74" s="137" t="n"/>
+      <c r="A74" s="138" t="n"/>
       <c r="B74" s="49" t="n"/>
       <c r="C74" s="49" t="n"/>
       <c r="D74" s="49" t="n"/>
@@ -26731,12 +26740,12 @@
       <c r="H74" s="49" t="n"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="135" t="inlineStr">
+      <c r="A75" s="136" t="inlineStr">
         <is>
           <t>Note 15</t>
         </is>
       </c>
-      <c r="B75" s="136" t="inlineStr">
+      <c r="B75" s="137" t="inlineStr">
         <is>
           <t>DOTATION</t>
         </is>
@@ -26749,7 +26758,7 @@
       <c r="H75" s="49" t="n"/>
     </row>
     <row r="76" ht="110" customHeight="1">
-      <c r="A76" s="137" t="n"/>
+      <c r="A76" s="138" t="n"/>
       <c r="B76" s="49" t="n"/>
       <c r="C76" s="49" t="n"/>
       <c r="D76" s="49" t="n"/>
@@ -26759,12 +26768,12 @@
       <c r="H76" s="49" t="n"/>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="135" t="inlineStr">
+      <c r="A77" s="136" t="inlineStr">
         <is>
           <t>Note 16</t>
         </is>
       </c>
-      <c r="B77" s="136" t="inlineStr">
+      <c r="B77" s="137" t="inlineStr">
         <is>
           <t>RÉSERVES</t>
         </is>
@@ -26777,7 +26786,7 @@
       <c r="H77" s="49" t="n"/>
     </row>
     <row r="78" ht="110" customHeight="1">
-      <c r="A78" s="137" t="n"/>
+      <c r="A78" s="138" t="n"/>
       <c r="B78" s="49" t="n"/>
       <c r="C78" s="49" t="n"/>
       <c r="D78" s="49" t="n"/>
@@ -26787,12 +26796,12 @@
       <c r="H78" s="49" t="n"/>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="135" t="inlineStr">
+      <c r="A79" s="136" t="inlineStr">
         <is>
           <t>Note 17A</t>
         </is>
       </c>
-      <c r="B79" s="136" t="inlineStr">
+      <c r="B79" s="137" t="inlineStr">
         <is>
           <t>SUBVENTIONS ET PROVISIONS RÉGLEMENTÉES</t>
         </is>
@@ -26805,7 +26814,7 @@
       <c r="H79" s="49" t="n"/>
     </row>
     <row r="80" ht="110" customHeight="1">
-      <c r="A80" s="137" t="n"/>
+      <c r="A80" s="138" t="n"/>
       <c r="B80" s="49" t="n"/>
       <c r="C80" s="49" t="n"/>
       <c r="D80" s="49" t="n"/>
@@ -26820,7 +26829,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G81" s="132" t="inlineStr">
+      <c r="G81" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 7/12</t>
@@ -26872,12 +26881,12 @@
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="135" t="inlineStr">
+      <c r="A86" s="136" t="inlineStr">
         <is>
           <t>Note 17B</t>
         </is>
       </c>
-      <c r="B86" s="136" t="inlineStr">
+      <c r="B86" s="137" t="inlineStr">
         <is>
           <t>FONDS AFFECTÉS ET REPORTÉS</t>
         </is>
@@ -26890,7 +26899,7 @@
       <c r="H86" s="49" t="n"/>
     </row>
     <row r="87" ht="110" customHeight="1">
-      <c r="A87" s="137" t="n"/>
+      <c r="A87" s="138" t="n"/>
       <c r="B87" s="49" t="n"/>
       <c r="C87" s="49" t="n"/>
       <c r="D87" s="49" t="n"/>
@@ -26900,12 +26909,12 @@
       <c r="H87" s="49" t="n"/>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="135" t="inlineStr">
+      <c r="A88" s="136" t="inlineStr">
         <is>
           <t>Note 18A</t>
         </is>
       </c>
-      <c r="B88" s="136" t="inlineStr">
+      <c r="B88" s="137" t="inlineStr">
         <is>
           <t>DETTES FINANCIÈRES ET RESSOURCES ASSIMILÉES</t>
         </is>
@@ -26918,7 +26927,7 @@
       <c r="H88" s="49" t="n"/>
     </row>
     <row r="89" ht="110" customHeight="1">
-      <c r="A89" s="137" t="n"/>
+      <c r="A89" s="138" t="n"/>
       <c r="B89" s="49" t="n"/>
       <c r="C89" s="49" t="n"/>
       <c r="D89" s="49" t="n"/>
@@ -26928,12 +26937,12 @@
       <c r="H89" s="49" t="n"/>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="135" t="inlineStr">
+      <c r="A90" s="136" t="inlineStr">
         <is>
           <t>Note 18B</t>
         </is>
       </c>
-      <c r="B90" s="136" t="inlineStr">
+      <c r="B90" s="137" t="inlineStr">
         <is>
           <t>ACTIFS ET PASSIFS ÉVENTUELS</t>
         </is>
@@ -26946,7 +26955,7 @@
       <c r="H90" s="49" t="n"/>
     </row>
     <row r="91" ht="110" customHeight="1">
-      <c r="A91" s="137" t="n"/>
+      <c r="A91" s="138" t="n"/>
       <c r="B91" s="49" t="n"/>
       <c r="C91" s="49" t="n"/>
       <c r="D91" s="49" t="n"/>
@@ -26956,12 +26965,12 @@
       <c r="H91" s="49" t="n"/>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="135" t="inlineStr">
+      <c r="A92" s="136" t="inlineStr">
         <is>
           <t>Note 19</t>
         </is>
       </c>
-      <c r="B92" s="136" t="inlineStr">
+      <c r="B92" s="137" t="inlineStr">
         <is>
           <t>FOURNISSEURS D'EXPLOITATION</t>
         </is>
@@ -26974,7 +26983,7 @@
       <c r="H92" s="49" t="n"/>
     </row>
     <row r="93" ht="110" customHeight="1">
-      <c r="A93" s="137" t="n"/>
+      <c r="A93" s="138" t="n"/>
       <c r="B93" s="49" t="n"/>
       <c r="C93" s="49" t="n"/>
       <c r="D93" s="49" t="n"/>
@@ -26989,7 +26998,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G94" s="132" t="inlineStr">
+      <c r="G94" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 8/12</t>
@@ -27041,12 +27050,12 @@
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="135" t="inlineStr">
+      <c r="A99" s="136" t="inlineStr">
         <is>
           <t>Note 20</t>
         </is>
       </c>
-      <c r="B99" s="136" t="inlineStr">
+      <c r="B99" s="137" t="inlineStr">
         <is>
           <t>DETTES FISCALES ET SOCIALES</t>
         </is>
@@ -27059,7 +27068,7 @@
       <c r="H99" s="49" t="n"/>
     </row>
     <row r="100" ht="110" customHeight="1">
-      <c r="A100" s="137" t="n"/>
+      <c r="A100" s="138" t="n"/>
       <c r="B100" s="49" t="n"/>
       <c r="C100" s="49" t="n"/>
       <c r="D100" s="49" t="n"/>
@@ -27069,12 +27078,12 @@
       <c r="H100" s="49" t="n"/>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="135" t="inlineStr">
+      <c r="A101" s="136" t="inlineStr">
         <is>
           <t>Note 21</t>
         </is>
       </c>
-      <c r="B101" s="136" t="inlineStr">
+      <c r="B101" s="137" t="inlineStr">
         <is>
           <t>AUTRES DETTES ET PROVISIONS POUR RISQUES ET CHARGES À COURT TERME</t>
         </is>
@@ -27087,7 +27096,7 @@
       <c r="H101" s="49" t="n"/>
     </row>
     <row r="102" ht="110" customHeight="1">
-      <c r="A102" s="137" t="n"/>
+      <c r="A102" s="138" t="n"/>
       <c r="B102" s="49" t="n"/>
       <c r="C102" s="49" t="n"/>
       <c r="D102" s="49" t="n"/>
@@ -27097,12 +27106,12 @@
       <c r="H102" s="49" t="n"/>
     </row>
     <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="135" t="inlineStr">
+      <c r="A103" s="136" t="inlineStr">
         <is>
           <t>Note 22</t>
         </is>
       </c>
-      <c r="B103" s="136" t="inlineStr">
+      <c r="B103" s="137" t="inlineStr">
         <is>
           <t>BANQUES, CRÉDIT D'ESCOMPTE ET DE TRÉSORERIE</t>
         </is>
@@ -27115,7 +27124,7 @@
       <c r="H103" s="49" t="n"/>
     </row>
     <row r="104" ht="110" customHeight="1">
-      <c r="A104" s="137" t="n"/>
+      <c r="A104" s="138" t="n"/>
       <c r="B104" s="49" t="n"/>
       <c r="C104" s="49" t="n"/>
       <c r="D104" s="49" t="n"/>
@@ -27125,26 +27134,26 @@
       <c r="H104" s="49" t="n"/>
     </row>
     <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="133" t="inlineStr">
+      <c r="A105" s="134" t="inlineStr">
         <is>
           <t>Partie 3 : Notes sur le compte de résultat</t>
         </is>
       </c>
-      <c r="B105" s="134" t="n"/>
-      <c r="C105" s="134" t="n"/>
-      <c r="D105" s="134" t="n"/>
-      <c r="E105" s="134" t="n"/>
-      <c r="F105" s="134" t="n"/>
-      <c r="G105" s="134" t="n"/>
-      <c r="H105" s="134" t="n"/>
+      <c r="B105" s="135" t="n"/>
+      <c r="C105" s="135" t="n"/>
+      <c r="D105" s="135" t="n"/>
+      <c r="E105" s="135" t="n"/>
+      <c r="F105" s="135" t="n"/>
+      <c r="G105" s="135" t="n"/>
+      <c r="H105" s="135" t="n"/>
     </row>
     <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="135" t="inlineStr">
+      <c r="A106" s="136" t="inlineStr">
         <is>
           <t>Note 23</t>
         </is>
       </c>
-      <c r="B106" s="136" t="inlineStr">
+      <c r="B106" s="137" t="inlineStr">
         <is>
           <t>REVENUS ET AUTRES PRODUITS</t>
         </is>
@@ -27157,7 +27166,7 @@
       <c r="H106" s="49" t="n"/>
     </row>
     <row r="107" ht="110" customHeight="1">
-      <c r="A107" s="137" t="n"/>
+      <c r="A107" s="138" t="n"/>
       <c r="B107" s="49" t="n"/>
       <c r="C107" s="49" t="n"/>
       <c r="D107" s="49" t="n"/>
@@ -27172,7 +27181,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G108" s="132" t="inlineStr">
+      <c r="G108" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 9/12</t>
@@ -27224,12 +27233,12 @@
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="135" t="inlineStr">
+      <c r="A113" s="136" t="inlineStr">
         <is>
           <t>Note 24</t>
         </is>
       </c>
-      <c r="B113" s="136" t="inlineStr">
+      <c r="B113" s="137" t="inlineStr">
         <is>
           <t>ACHATS</t>
         </is>
@@ -27242,7 +27251,7 @@
       <c r="H113" s="49" t="n"/>
     </row>
     <row r="114" ht="110" customHeight="1">
-      <c r="A114" s="137" t="n"/>
+      <c r="A114" s="138" t="n"/>
       <c r="B114" s="49" t="n"/>
       <c r="C114" s="49" t="n"/>
       <c r="D114" s="49" t="n"/>
@@ -27252,12 +27261,12 @@
       <c r="H114" s="49" t="n"/>
     </row>
     <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="135" t="inlineStr">
+      <c r="A115" s="136" t="inlineStr">
         <is>
           <t>Note 25</t>
         </is>
       </c>
-      <c r="B115" s="136" t="inlineStr">
+      <c r="B115" s="137" t="inlineStr">
         <is>
           <t>TRANSPORTS</t>
         </is>
@@ -27270,7 +27279,7 @@
       <c r="H115" s="49" t="n"/>
     </row>
     <row r="116" ht="110" customHeight="1">
-      <c r="A116" s="137" t="n"/>
+      <c r="A116" s="138" t="n"/>
       <c r="B116" s="49" t="n"/>
       <c r="C116" s="49" t="n"/>
       <c r="D116" s="49" t="n"/>
@@ -27280,12 +27289,12 @@
       <c r="H116" s="49" t="n"/>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="135" t="inlineStr">
+      <c r="A117" s="136" t="inlineStr">
         <is>
           <t>Note 26</t>
         </is>
       </c>
-      <c r="B117" s="136" t="inlineStr">
+      <c r="B117" s="137" t="inlineStr">
         <is>
           <t>SERVICES EXTÉRIEURS</t>
         </is>
@@ -27298,7 +27307,7 @@
       <c r="H117" s="49" t="n"/>
     </row>
     <row r="118" ht="110" customHeight="1">
-      <c r="A118" s="137" t="n"/>
+      <c r="A118" s="138" t="n"/>
       <c r="B118" s="49" t="n"/>
       <c r="C118" s="49" t="n"/>
       <c r="D118" s="49" t="n"/>
@@ -27308,12 +27317,12 @@
       <c r="H118" s="49" t="n"/>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="135" t="inlineStr">
+      <c r="A119" s="136" t="inlineStr">
         <is>
           <t>Note 27</t>
         </is>
       </c>
-      <c r="B119" s="136" t="inlineStr">
+      <c r="B119" s="137" t="inlineStr">
         <is>
           <t>IMPÔTS ET TAXES</t>
         </is>
@@ -27326,7 +27335,7 @@
       <c r="H119" s="49" t="n"/>
     </row>
     <row r="120" ht="110" customHeight="1">
-      <c r="A120" s="137" t="n"/>
+      <c r="A120" s="138" t="n"/>
       <c r="B120" s="49" t="n"/>
       <c r="C120" s="49" t="n"/>
       <c r="D120" s="49" t="n"/>
@@ -27341,7 +27350,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G121" s="132" t="inlineStr">
+      <c r="G121" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 10/12</t>
@@ -27393,12 +27402,12 @@
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="135" t="inlineStr">
+      <c r="A126" s="136" t="inlineStr">
         <is>
           <t>Note 28</t>
         </is>
       </c>
-      <c r="B126" s="136" t="inlineStr">
+      <c r="B126" s="137" t="inlineStr">
         <is>
           <t>AUTRES CHARGES</t>
         </is>
@@ -27411,7 +27420,7 @@
       <c r="H126" s="49" t="n"/>
     </row>
     <row r="127" ht="110" customHeight="1">
-      <c r="A127" s="137" t="n"/>
+      <c r="A127" s="138" t="n"/>
       <c r="B127" s="49" t="n"/>
       <c r="C127" s="49" t="n"/>
       <c r="D127" s="49" t="n"/>
@@ -27421,12 +27430,12 @@
       <c r="H127" s="49" t="n"/>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="135" t="inlineStr">
+      <c r="A128" s="136" t="inlineStr">
         <is>
           <t>Note 29A</t>
         </is>
       </c>
-      <c r="B128" s="136" t="inlineStr">
+      <c r="B128" s="137" t="inlineStr">
         <is>
           <t>CHARGES DE PERSONNEL</t>
         </is>
@@ -27439,7 +27448,7 @@
       <c r="H128" s="49" t="n"/>
     </row>
     <row r="129" ht="110" customHeight="1">
-      <c r="A129" s="137" t="n"/>
+      <c r="A129" s="138" t="n"/>
       <c r="B129" s="49" t="n"/>
       <c r="C129" s="49" t="n"/>
       <c r="D129" s="49" t="n"/>
@@ -27449,12 +27458,12 @@
       <c r="H129" s="49" t="n"/>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="135" t="inlineStr">
+      <c r="A130" s="136" t="inlineStr">
         <is>
           <t>Note 29B</t>
         </is>
       </c>
-      <c r="B130" s="136" t="inlineStr">
+      <c r="B130" s="137" t="inlineStr">
         <is>
           <t>EFFECTIFS, MASSE SALARIALE ET PERSONNEL EXTÉRIEUR</t>
         </is>
@@ -27467,7 +27476,7 @@
       <c r="H130" s="49" t="n"/>
     </row>
     <row r="131" ht="110" customHeight="1">
-      <c r="A131" s="137" t="n"/>
+      <c r="A131" s="138" t="n"/>
       <c r="B131" s="49" t="n"/>
       <c r="C131" s="49" t="n"/>
       <c r="D131" s="49" t="n"/>
@@ -27477,12 +27486,12 @@
       <c r="H131" s="49" t="n"/>
     </row>
     <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="135" t="inlineStr">
+      <c r="A132" s="136" t="inlineStr">
         <is>
           <t>Note 30</t>
         </is>
       </c>
-      <c r="B132" s="136" t="inlineStr">
+      <c r="B132" s="137" t="inlineStr">
         <is>
           <t>DOTATIONS ET CHARGES POUR PROVISIONS ET DÉPRÉCIATIONS</t>
         </is>
@@ -27495,7 +27504,7 @@
       <c r="H132" s="49" t="n"/>
     </row>
     <row r="133" ht="110" customHeight="1">
-      <c r="A133" s="137" t="n"/>
+      <c r="A133" s="138" t="n"/>
       <c r="B133" s="49" t="n"/>
       <c r="C133" s="49" t="n"/>
       <c r="D133" s="49" t="n"/>
@@ -27510,7 +27519,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G134" s="132" t="inlineStr">
+      <c r="G134" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 11/12</t>
@@ -27562,12 +27571,12 @@
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="135" t="inlineStr">
+      <c r="A139" s="136" t="inlineStr">
         <is>
           <t>Note 31</t>
         </is>
       </c>
-      <c r="B139" s="136" t="inlineStr">
+      <c r="B139" s="137" t="inlineStr">
         <is>
           <t>CHARGES ET REVENUS FINANCIERS</t>
         </is>
@@ -27580,7 +27589,7 @@
       <c r="H139" s="49" t="n"/>
     </row>
     <row r="140" ht="110" customHeight="1">
-      <c r="A140" s="137" t="n"/>
+      <c r="A140" s="138" t="n"/>
       <c r="B140" s="49" t="n"/>
       <c r="C140" s="49" t="n"/>
       <c r="D140" s="49" t="n"/>
@@ -27590,12 +27599,12 @@
       <c r="H140" s="49" t="n"/>
     </row>
     <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="135" t="inlineStr">
+      <c r="A141" s="136" t="inlineStr">
         <is>
           <t>Note 32</t>
         </is>
       </c>
-      <c r="B141" s="136" t="inlineStr">
+      <c r="B141" s="137" t="inlineStr">
         <is>
           <t>AUTRES CHARGES ET PRODUITS HAO</t>
         </is>
@@ -27608,7 +27617,7 @@
       <c r="H141" s="49" t="n"/>
     </row>
     <row r="142" ht="110" customHeight="1">
-      <c r="A142" s="137" t="n"/>
+      <c r="A142" s="138" t="n"/>
       <c r="B142" s="49" t="n"/>
       <c r="C142" s="49" t="n"/>
       <c r="D142" s="49" t="n"/>
@@ -27618,26 +27627,26 @@
       <c r="H142" s="49" t="n"/>
     </row>
     <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="133" t="inlineStr">
+      <c r="A143" s="134" t="inlineStr">
         <is>
           <t>Partie 4 : Autres informations</t>
         </is>
       </c>
-      <c r="B143" s="134" t="n"/>
-      <c r="C143" s="134" t="n"/>
-      <c r="D143" s="134" t="n"/>
-      <c r="E143" s="134" t="n"/>
-      <c r="F143" s="134" t="n"/>
-      <c r="G143" s="134" t="n"/>
-      <c r="H143" s="134" t="n"/>
+      <c r="B143" s="135" t="n"/>
+      <c r="C143" s="135" t="n"/>
+      <c r="D143" s="135" t="n"/>
+      <c r="E143" s="135" t="n"/>
+      <c r="F143" s="135" t="n"/>
+      <c r="G143" s="135" t="n"/>
+      <c r="H143" s="135" t="n"/>
     </row>
     <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="135" t="inlineStr">
+      <c r="A144" s="136" t="inlineStr">
         <is>
           <t>Note 33</t>
         </is>
       </c>
-      <c r="B144" s="136" t="inlineStr">
+      <c r="B144" s="137" t="inlineStr">
         <is>
           <t>FICHE DE SYNTHÈSE DES PRINCIPAUX INDICATEURS FINANCIERS</t>
         </is>
@@ -27650,7 +27659,7 @@
       <c r="H144" s="49" t="n"/>
     </row>
     <row r="145" ht="110" customHeight="1">
-      <c r="A145" s="137" t="n"/>
+      <c r="A145" s="138" t="n"/>
       <c r="B145" s="49" t="n"/>
       <c r="C145" s="49" t="n"/>
       <c r="D145" s="49" t="n"/>
@@ -27660,12 +27669,12 @@
       <c r="H145" s="49" t="n"/>
     </row>
     <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="135" t="inlineStr">
+      <c r="A146" s="136" t="inlineStr">
         <is>
           <t>Note 34</t>
         </is>
       </c>
-      <c r="B146" s="136" t="inlineStr">
+      <c r="B146" s="137" t="inlineStr">
         <is>
           <t>LISTE DES INFORMATIONS SOCIALES, ENVIRONNEMENTALES ET SOCIÉTALES</t>
         </is>
@@ -27678,7 +27687,7 @@
       <c r="H146" s="49" t="n"/>
     </row>
     <row r="147" ht="110" customHeight="1">
-      <c r="A147" s="137" t="n"/>
+      <c r="A147" s="138" t="n"/>
       <c r="B147" s="49" t="n"/>
       <c r="C147" s="49" t="n"/>
       <c r="D147" s="49" t="n"/>
@@ -27693,7 +27702,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G148" s="132" t="inlineStr">
+      <c r="G148" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 12/12</t>
@@ -27745,12 +27754,12 @@
       </c>
     </row>
     <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="135" t="inlineStr">
+      <c r="A153" s="136" t="inlineStr">
         <is>
           <t>Note 35</t>
         </is>
       </c>
-      <c r="B153" s="136" t="inlineStr">
+      <c r="B153" s="137" t="inlineStr">
         <is>
           <t>TABLEAU D'EXÉCUTION BUDGÉTAIRE</t>
         </is>
@@ -27763,7 +27772,7 @@
       <c r="H153" s="49" t="n"/>
     </row>
     <row r="154" ht="110" customHeight="1">
-      <c r="A154" s="137" t="n"/>
+      <c r="A154" s="138" t="n"/>
       <c r="B154" s="49" t="n"/>
       <c r="C154" s="49" t="n"/>
       <c r="D154" s="49" t="n"/>
@@ -28023,7 +28032,7 @@
       <c r="F10" s="61" t="n"/>
       <c r="G10" s="62" t="inlineStr">
         <is>
-          <t>DU : 01-01-2025    AU : 31-12-2025</t>
+          <t>DU :     AU : 31-12-2025</t>
         </is>
       </c>
       <c r="H10" s="61" t="n"/>
@@ -31492,7 +31501,7 @@
       </c>
       <c r="C12" s="90" t="inlineStr"/>
       <c r="D12" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -31504,7 +31513,7 @@
         <v/>
       </c>
       <c r="G12" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31558,11 +31567,11 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F14" s="5">
@@ -31570,7 +31579,7 @@
         <v/>
       </c>
       <c r="G14" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31591,7 +31600,7 @@
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F15" s="5">
@@ -31599,7 +31608,7 @@
         <v/>
       </c>
       <c r="G15" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31706,11 +31715,11 @@
       </c>
       <c r="C19" s="90" t="inlineStr"/>
       <c r="D19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F19" s="5">
@@ -31718,7 +31727,7 @@
         <v/>
       </c>
       <c r="G19" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31735,11 +31744,11 @@
       </c>
       <c r="C20" s="90" t="inlineStr"/>
       <c r="D20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F20" s="5">
@@ -31747,7 +31756,7 @@
         <v/>
       </c>
       <c r="G20" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31768,7 +31777,7 @@
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -31776,7 +31785,7 @@
         <v/>
       </c>
       <c r="G21" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31797,7 +31806,7 @@
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -31805,7 +31814,7 @@
         <v/>
       </c>
       <c r="G22" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32008,7 +32017,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -32020,7 +32029,7 @@
         <v/>
       </c>
       <c r="G29" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32107,11 +32116,11 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -32119,7 +32128,7 @@
         <v/>
       </c>
       <c r="G32" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32235,11 +32244,11 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -32247,7 +32256,7 @@
         <v/>
       </c>
       <c r="G36" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>

--- a/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
+++ b/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
@@ -3427,11 +3427,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3544,11 +3544,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3619,11 +3619,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
         <v/>
       </c>
     </row>
@@ -4007,11 +4007,11 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E14" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4057,11 +4057,11 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E16" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4203,11 +4203,11 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E22" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4228,11 +4228,11 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E23" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4278,11 +4278,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4403,11 +4403,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4495,11 +4495,11 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E34" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="D9" s="101">
-        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E9" s="102" t="n"/>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D25" s="84">
-        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
+        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
         <v/>
       </c>
       <c r="E25" s="85" t="n"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="D34" s="9">
-        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
+        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
         <v/>
       </c>
       <c r="E34" s="82" t="n"/>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="D35" s="101">
-        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))))-D9</f>
+        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))))-D9</f>
         <v/>
       </c>
       <c r="E35" s="102" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="B13" s="119" t="inlineStr"/>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D13" s="120" t="n"/>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B17" s="119" t="inlineStr"/>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="C26" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D26" s="120" t="n"/>
@@ -7607,15 +7607,15 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E11" s="120">
@@ -7947,15 +7947,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -8096,15 +8096,15 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E17" s="120">
@@ -8119,15 +8119,15 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E18" s="120">
@@ -8142,15 +8142,15 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E19" s="120">
@@ -9354,15 +9354,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2416*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2426*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2446*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2416*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2426*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2446*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -9796,15 +9796,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -9899,15 +9899,15 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E15" s="120">
@@ -11694,11 +11694,11 @@
         </is>
       </c>
       <c r="B21" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C21" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D21" s="120">
@@ -11988,11 +11988,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -13179,11 +13179,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -13205,11 +13205,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -13257,11 +13257,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -14337,11 +14337,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -14452,11 +14452,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -15894,11 +15894,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -16584,11 +16584,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -17451,11 +17451,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -17959,11 +17959,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -18141,11 +18141,11 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"442*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"446*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"446*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"442*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"442*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"446*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"442*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D19" s="120">
@@ -18167,11 +18167,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -18219,11 +18219,11 @@
         </is>
       </c>
       <c r="B22" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"449*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"448*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"448*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"449*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C22" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"449*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"448*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"448*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"449*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D22" s="120">
@@ -18590,11 +18590,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -18694,11 +18694,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4721*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4721*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4721*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4721*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -19011,11 +19011,11 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D11" s="120">
@@ -19374,11 +19374,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -19443,11 +19443,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -22878,17 +22878,17 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="120" t="n"/>
       <c r="F17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="G17" s="120" t="n"/>
@@ -24678,11 +24678,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -31501,7 +31501,7 @@
       </c>
       <c r="C12" s="90" t="inlineStr"/>
       <c r="D12" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -31513,7 +31513,7 @@
         <v/>
       </c>
       <c r="G12" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31567,11 +31567,11 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F14" s="5">
@@ -31579,7 +31579,7 @@
         <v/>
       </c>
       <c r="G14" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31600,7 +31600,7 @@
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F15" s="5">
@@ -31608,7 +31608,7 @@
         <v/>
       </c>
       <c r="G15" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31715,11 +31715,11 @@
       </c>
       <c r="C19" s="90" t="inlineStr"/>
       <c r="D19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F19" s="5">
@@ -31727,7 +31727,7 @@
         <v/>
       </c>
       <c r="G19" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31744,11 +31744,11 @@
       </c>
       <c r="C20" s="90" t="inlineStr"/>
       <c r="D20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F20" s="5">
@@ -31756,7 +31756,7 @@
         <v/>
       </c>
       <c r="G20" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -31785,7 +31785,7 @@
         <v/>
       </c>
       <c r="G21" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31806,7 +31806,7 @@
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -31814,7 +31814,7 @@
         <v/>
       </c>
       <c r="G22" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32017,7 +32017,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -32029,7 +32029,7 @@
         <v/>
       </c>
       <c r="G29" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32116,11 +32116,11 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -32128,7 +32128,7 @@
         <v/>
       </c>
       <c r="G32" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32244,11 +32244,11 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -32256,7 +32256,7 @@
         <v/>
       </c>
       <c r="G36" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>

--- a/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
+++ b/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
@@ -3427,11 +3427,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3544,11 +3544,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3619,11 +3619,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
         <v/>
       </c>
     </row>
@@ -3665,11 +3665,11 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E35" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68))</f>
         <v/>
       </c>
     </row>
@@ -4057,11 +4057,11 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E16" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4203,11 +4203,11 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E22" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4278,11 +4278,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4403,11 +4403,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4470,11 +4470,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4495,11 +4495,11 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E34" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="D9" s="101">
-        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E9" s="102" t="n"/>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D25" s="84">
-        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
+        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
         <v/>
       </c>
       <c r="E25" s="85" t="n"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="D34" s="9">
-        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
+        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
         <v/>
       </c>
       <c r="E34" s="82" t="n"/>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="D35" s="101">
-        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))))-D9</f>
+        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))))-D9</f>
         <v/>
       </c>
       <c r="E35" s="102" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="B13" s="119" t="inlineStr"/>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D13" s="120" t="n"/>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B17" s="119" t="inlineStr"/>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="C26" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D26" s="120" t="n"/>
@@ -7607,15 +7607,15 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2012*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2013*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2012*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2013*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E11" s="120">
@@ -7630,15 +7630,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -7947,15 +7947,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -8096,15 +8096,15 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E17" s="120">
@@ -8119,15 +8119,15 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E18" s="120">
@@ -8142,15 +8142,15 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E19" s="120">
@@ -8340,7 +8340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8410,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0</v>
@@ -8440,13 +8440,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0</v>
@@ -8500,10 +8500,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -8512,7 +8512,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8530,10 +8530,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>4400000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -8560,13 +8560,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -8590,10 +8590,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
@@ -8620,13 +8620,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>0</v>
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>3200000</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
@@ -8740,13 +8740,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
@@ -8770,13 +8770,13 @@
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -8800,13 +8800,13 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>1450000</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
@@ -8860,13 +8860,13 @@
         <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
@@ -8887,13 +8887,13 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
@@ -8920,13 +8920,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -8950,13 +8950,13 @@
         <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -8980,13 +8980,13 @@
         <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -9010,13 +9010,13 @@
         <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -9040,13 +9040,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -9067,13 +9067,13 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0</v>
+        <v>4020000</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
@@ -9097,13 +9097,13 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>0</v>
@@ -9115,60 +9115,750 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Achats de biens et services liés à l'activité</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Matières et fournitures consommables</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Eau, électricité et autres achats non stockés</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>620000</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>620000</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Transport du personnel</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Locations et charges locatives</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Frais de télécommunications</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Frais de recherche de fonds</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Impôts et taxes directs</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Subventions accordées par l'entité</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Dons en nature courants à distribuer</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Rémunérations directes personnel national</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>4070000</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>4070000</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Charges sociales</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>640000</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>640000</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Intérêts des emprunts</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>210000</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>210000</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Dotations amortissements incorporelles</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>6813</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Dotations amortissements corporelles</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>550000</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>550000</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Dotations aux provisions d'exploitation</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Cotisations des adhérents</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>7041</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Dons</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>7046</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Mécénats</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>7051</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Ventes de marchandises</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Revenus des manifestations</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>950000</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Subventions d'exploitation - État</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>4600000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Produits divers</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="C26" s="7">
-        <f>SUM(C2:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="7">
-        <f>SUM(D2:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="7">
-        <f>SUM(E2:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="7">
-        <f>SUM(F2:F25)</f>
-        <v/>
-      </c>
-      <c r="G26" s="7">
-        <f>SUM(G2:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="7">
-        <f>SUM(H2:H25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="C49" s="7">
+        <f>SUM(C2:C48)</f>
+        <v/>
+      </c>
+      <c r="D49" s="7">
+        <f>SUM(D2:D48)</f>
+        <v/>
+      </c>
+      <c r="E49" s="7">
+        <f>SUM(E2:E48)</f>
+        <v/>
+      </c>
+      <c r="F49" s="7">
+        <f>SUM(F2:F48)</f>
+        <v/>
+      </c>
+      <c r="G49" s="7">
+        <f>SUM(G2:G48)</f>
+        <v/>
+      </c>
+      <c r="H49" s="7">
+        <f>SUM(H2:H48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Contrôle d'équilibre par solde (débit - crédit, doit être 0)</t>
         </is>
       </c>
-      <c r="C27" s="9">
-        <f>C26-D26</f>
-        <v/>
-      </c>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9">
-        <f>E26-F26</f>
-        <v/>
-      </c>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9">
-        <f>G26-H26</f>
-        <v/>
-      </c>
-      <c r="H27" s="9" t="n"/>
+      <c r="C50" s="9">
+        <f>C49-D49</f>
+        <v/>
+      </c>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9">
+        <f>E49-F49</f>
+        <v/>
+      </c>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9">
+        <f>G49-H49</f>
+        <v/>
+      </c>
+      <c r="H50" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9796,15 +10486,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -9899,15 +10589,15 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E15" s="120">
@@ -9922,15 +10612,15 @@
         </is>
       </c>
       <c r="B16" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E16" s="120">
@@ -11694,11 +12384,11 @@
         </is>
       </c>
       <c r="B21" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C21" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D21" s="120">
@@ -12611,11 +13301,11 @@
         </is>
       </c>
       <c r="B21" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"419*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4192*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4191*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"419*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4191*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4192*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C21" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"419*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4192*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4191*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"419*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4191*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4192*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D21" s="120">
@@ -12844,27 +13534,27 @@
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="16" t="n"/>
       <c r="B6" s="17">
-        <f>SUM('BALANCE N-1'!C2:C25)</f>
+        <f>SUM('BALANCE N-1'!C2:C48)</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>SUM('BALANCE N-1'!D2:D25)</f>
+        <f>SUM('BALANCE N-1'!D2:D48)</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>SUM('BALANCE N-1'!E2:E25)</f>
+        <f>SUM('BALANCE N-1'!E2:E48)</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>SUM('BALANCE N-1'!F2:F25)</f>
+        <f>SUM('BALANCE N-1'!F2:F48)</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>SUM('BALANCE N-1'!G2:G25)</f>
+        <f>SUM('BALANCE N-1'!G2:G48)</f>
         <v/>
       </c>
       <c r="G6" s="18">
-        <f>SUM('BALANCE N-1'!H2:H25)</f>
+        <f>SUM('BALANCE N-1'!H2:H48)</f>
         <v/>
       </c>
     </row>
@@ -13179,11 +13869,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -13205,11 +13895,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -13257,11 +13947,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -14337,11 +15027,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -14452,11 +15142,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -15894,11 +16584,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -16584,11 +17274,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -17451,11 +18141,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4011*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4013*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4011*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4013*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -17669,11 +18359,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4094*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4098*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4098*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4094*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4094*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4098*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4098*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4094*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -17959,11 +18649,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -18167,11 +18857,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -18219,11 +18909,11 @@
         </is>
       </c>
       <c r="B22" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"448*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"449*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"449*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"448*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C22" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"448*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"449*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"449*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"448*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D22" s="120">
@@ -18590,11 +19280,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -18694,11 +19384,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4721*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4721*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4721*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4721*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -19011,11 +19701,11 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D11" s="120">
@@ -19057,11 +19747,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"561*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"561*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"561*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"561*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -19374,11 +20064,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -19443,11 +20133,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -20154,11 +20844,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -22878,17 +23568,17 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="120" t="n"/>
       <c r="F17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="G17" s="120" t="n"/>
@@ -24678,11 +25368,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -31501,7 +32191,7 @@
       </c>
       <c r="C12" s="90" t="inlineStr"/>
       <c r="D12" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -31513,7 +32203,7 @@
         <v/>
       </c>
       <c r="G12" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31567,11 +32257,11 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F14" s="5">
@@ -31579,7 +32269,7 @@
         <v/>
       </c>
       <c r="G14" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31600,7 +32290,7 @@
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F15" s="5">
@@ -31608,7 +32298,7 @@
         <v/>
       </c>
       <c r="G15" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31715,11 +32405,11 @@
       </c>
       <c r="C19" s="90" t="inlineStr"/>
       <c r="D19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F19" s="5">
@@ -31727,7 +32417,7 @@
         <v/>
       </c>
       <c r="G19" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -31744,11 +32434,11 @@
       </c>
       <c r="C20" s="90" t="inlineStr"/>
       <c r="D20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F20" s="5">
@@ -31756,7 +32446,7 @@
         <v/>
       </c>
       <c r="G20" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32017,7 +32707,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -32029,7 +32719,7 @@
         <v/>
       </c>
       <c r="G29" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32116,11 +32806,11 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -32128,7 +32818,7 @@
         <v/>
       </c>
       <c r="G32" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32244,11 +32934,11 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -32256,7 +32946,7 @@
         <v/>
       </c>
       <c r="G36" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>

--- a/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
+++ b/.claude/skills/sycebnl/liasse/exemples/exemple-etats-associations.xlsx
@@ -3427,11 +3427,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3544,11 +3544,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"481*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4861*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"481*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4861*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -3619,11 +3619,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"499*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"599*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"499*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"599*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"479*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68))</f>
         <v/>
       </c>
     </row>
@@ -3665,11 +3665,11 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E35" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68))</f>
         <v/>
       </c>
     </row>
@@ -4007,11 +4007,11 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7052*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"7053*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E14" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7052*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"7053*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4057,11 +4057,11 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"706*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E16" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"706*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4203,11 +4203,11 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"604*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"605*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"606*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"608*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E22" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"604*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"605*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"606*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"608*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4228,11 +4228,11 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6032*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6033*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6034*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"6035*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E23" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6032*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6033*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6034*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"6035*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4278,11 +4278,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"62*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"63*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"62*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"63*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4403,11 +4403,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4470,11 +4470,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"84*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"88*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"84*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"88*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4495,11 +4495,11 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"83*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"87*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E34" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"83*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"87*",'BALANCE N-1'!$G$2:$G$68))</f>
         <v/>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="D9" s="101">
-        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"50*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"590*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"51*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"591*",'BALANCE N-1'!$G$2:$G$68))))+(((SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)))))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"564*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$G$2:$G$68))+(SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E9" s="102" t="n"/>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D25" s="84">
-        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
+        <f>-((((SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"201*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2198*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"251*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"22*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"24*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"245*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2495*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"252*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"26*",'BALANCE N'!$H$2:$H$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"27*",'BALANCE N'!$H$2:$H$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"201*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"251*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"252*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"26*",'BALANCE N-1'!$H$2:$H$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"27*",'BALANCE N-1'!$H$2:$H$68)))))</f>
         <v/>
       </c>
       <c r="E25" s="85" t="n"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="D34" s="9">
-        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
+        <f>(((SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"181*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"182*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)))+((SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"19*",'BALANCE N'!$G$2:$G$68))))-(((SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"181*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"182*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"183*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"185*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"186*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"188*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)))+((SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"19*",'BALANCE N-1'!$G$2:$G$68))))</f>
         <v/>
       </c>
       <c r="E34" s="82" t="n"/>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="D35" s="101">
-        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68))))-D9</f>
+        <f>(((((SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"50*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"590*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"51*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"591*",'BALANCE N'!$G$2:$G$68))))+(((SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68)))-((SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"592*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"593*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"595*",'BALANCE N'!$G$2:$G$68)))))-((SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"564*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$G$2:$G$68))+(SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68))))-D9</f>
         <v/>
       </c>
       <c r="E35" s="102" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="B13" s="119" t="inlineStr"/>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"183*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"185*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"186*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"188*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D13" s="120" t="n"/>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B17" s="119" t="inlineStr"/>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="C26" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"479*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D26" s="120" t="n"/>
@@ -7630,15 +7630,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2014*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2017*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2014*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2017*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -7947,15 +7947,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"218*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -8096,15 +8096,15 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E17" s="120">
@@ -8119,15 +8119,15 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2315*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2325*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2315*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2325*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E18" s="120">
@@ -8142,15 +8142,15 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="D19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)))</f>
         <v/>
       </c>
       <c r="E19" s="120">
@@ -10486,15 +10486,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2817*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2817*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -10589,15 +10589,15 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E15" s="120">
@@ -10612,15 +10612,15 @@
         </is>
       </c>
       <c r="B16" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="E16" s="120">
@@ -12384,11 +12384,11 @@
         </is>
       </c>
       <c r="B21" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"484*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"488*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4998*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4881*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C21" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"484*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"488*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4998*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4881*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D21" s="120">
@@ -12678,11 +12678,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"35*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"35*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -13869,11 +13869,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"471*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"472*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"475*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"471*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"472*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"475*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -13895,11 +13895,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -13947,11 +13947,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -14958,11 +14958,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -15027,11 +15027,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"532*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"533*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"538*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"532*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"533*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"538*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -15587,11 +15587,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"101*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"102*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"101*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"102*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -16584,11 +16584,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"161*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"162*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"163*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"164*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"161*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"162*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"163*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"164*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -17274,11 +17274,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"187*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1871*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1872*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1873*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"1876*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"187*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1871*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1872*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1873*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"1876*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -18359,11 +18359,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4098*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4094*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4094*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4098*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4098*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4094*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4094*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4098*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -18649,11 +18649,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"421*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"423*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"424*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"425*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"427*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"428*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"4281*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"421*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"423*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"424*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"425*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"427*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"428*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"4281*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -18831,11 +18831,11 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"446*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"442*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"442*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"446*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"446*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"442*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"442*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"446*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D19" s="120">
@@ -18857,11 +18857,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"443*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"444*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"445*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"443*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"444*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"445*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -18909,11 +18909,11 @@
         </is>
       </c>
       <c r="B22" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"449*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"448*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"448*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"449*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C22" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"449*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"448*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"448*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"449*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D22" s="120">
@@ -19280,11 +19280,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"4711*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4712*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4717*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4719*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"4711*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4712*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4717*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4719*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -19384,11 +19384,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4721*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"473*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"474*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"476*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"477*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"4721*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4721*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"473*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"474*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"476*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"477*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"4721*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -19701,11 +19701,11 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"523*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"524*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"525*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"523*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"524*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"525*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D11" s="120">
@@ -19724,11 +19724,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"566*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"526*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"526*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"566*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"566*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"526*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"526*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"566*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -19747,11 +19747,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"561*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"561*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"565*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"561*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"561*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"565*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -20064,11 +20064,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"702*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"707*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"708*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"702*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"707*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"708*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -20133,11 +20133,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"72*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"73*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"75*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"77*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"78*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"72*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"73*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"75*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"77*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"78*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -20844,11 +20844,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"618*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"619*",'BALANCE N'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$H$2:$H$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"618*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"619*",'BALANCE N-1'!$H$2:$H$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -23568,17 +23568,17 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))-(SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="120" t="n"/>
       <c r="F17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68))-(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68)))</f>
         <v/>
       </c>
       <c r="G17" s="120" t="n"/>
@@ -25368,11 +25368,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
+        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"68*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"69*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"85*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"79*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"86*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"81*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"82*",'BALANCE N'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
+        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"68*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"69*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"85*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"79*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"86*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"81*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"82*",'BALANCE N-1'!$G$2:$G$68)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -32191,7 +32191,7 @@
       </c>
       <c r="C12" s="90" t="inlineStr"/>
       <c r="D12" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"202*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"203*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"204*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"205*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -32203,7 +32203,7 @@
         <v/>
       </c>
       <c r="G12" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"202*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"203*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"204*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"205*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2902*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32257,11 +32257,11 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"212*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"213*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"214*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2193*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2812*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2813*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2814*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2912*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2913*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F14" s="5">
@@ -32269,7 +32269,7 @@
         <v/>
       </c>
       <c r="G14" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"212*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"213*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"214*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2193*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2812*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2813*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2814*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2912*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2913*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32290,7 +32290,7 @@
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2818*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2918*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2919*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F15" s="5">
@@ -32298,7 +32298,7 @@
         <v/>
       </c>
       <c r="G15" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"218*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2198*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2818*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2918*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2919*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32380,7 +32380,7 @@
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"292*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"292*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"282*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"282*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"282*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"282*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"292*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"292*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F18" s="5">
@@ -32388,7 +32388,7 @@
         <v/>
       </c>
       <c r="G18" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"292*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"292*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"282*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"282*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"22*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"282*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"282*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"292*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"292*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32405,11 +32405,11 @@
       </c>
       <c r="C19" s="90" t="inlineStr"/>
       <c r="D19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"231*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"232*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"233*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2391*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2392*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2393*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2396*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2831*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2832*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2833*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2931*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2932*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2933*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F19" s="5">
@@ -32417,7 +32417,7 @@
         <v/>
       </c>
       <c r="G19" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"231*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"232*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"233*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2391*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2392*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2393*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2396*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2831*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2832*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2833*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2931*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2932*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2933*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32434,11 +32434,11 @@
       </c>
       <c r="C20" s="90" t="inlineStr"/>
       <c r="D20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"234*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"235*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"238*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2394*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2395*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2398*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2834*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2835*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2838*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2934*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2935*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2938*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2939*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F20" s="5">
@@ -32446,7 +32446,7 @@
         <v/>
       </c>
       <c r="G20" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"234*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"235*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"238*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2394*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2395*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2398*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2834*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2835*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2838*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2934*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2935*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2938*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2939*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32467,7 +32467,7 @@
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"284*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"294*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -32475,7 +32475,7 @@
         <v/>
       </c>
       <c r="G21" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"24*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"284*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"294*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32496,7 +32496,7 @@
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2845*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2945*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"2949*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -32504,7 +32504,7 @@
         <v/>
       </c>
       <c r="G22" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"245*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2495*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2845*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2945*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"2949*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32707,7 +32707,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"31*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"32*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"33*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"34*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"36*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"37*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"38*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -32719,7 +32719,7 @@
         <v/>
       </c>
       <c r="G29" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"31*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"32*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"33*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"34*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"36*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"37*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"38*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"39*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32806,11 +32806,11 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"42*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"43*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"44*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"45*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"46*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"47*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"478*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"492*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"493*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"494*",'BALANCE N'!$G$2:$G$68)+SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$H$2:$H$68)-SUMIF('BALANCE N'!$A$2:$A$68,"497*",'BALANCE N'!$G$2:$G$68))</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -32818,7 +32818,7 @@
         <v/>
       </c>
       <c r="G32" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"42*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"43*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"44*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"45*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"46*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"47*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"478*",'BALANCE N-1'!$G$2:$G$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"492*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"493*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"494*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"497*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"52*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"53*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"55*",'BALANCE N'!$H$2:$H$68)+SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$G$2:$G$68)-SUMIF('BALANCE N'!$A$2:$A$68,"57*",'BALANCE N'!$H$2:$H$68))</f>
         <v/>
       </c>
       <c r="E36" s="5">
@@ -32946,7 +32946,7 @@
         <v/>
       </c>
       <c r="G36" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"52*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"53*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"55*",'BALANCE N-1'!$H$2:$H$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$G$2:$G$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"57*",'BALANCE N-1'!$H$2:$H$68)))-((SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"592*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"593*",'BALANCE N-1'!$G$2:$G$68)+SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$H$2:$H$68)-SUMIF('BALANCE N-1'!$A$2:$A$68,"595*",'BALANCE N-1'!$G$2:$G$68)))</f>
         <v/>
       </c>
     </row>
